--- a/output/slowfix_all_markets_daily.xlsx
+++ b/output/slowfix_all_markets_daily.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -461,10 +461,11 @@
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -515,20 +516,25 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>data_end</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>open_at_end</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>win_rate_%</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>return_%</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>final_equity</t>
         </is>
@@ -570,12 +576,15 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>80</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="M2" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="M2" s="3" t="n">
+      <c r="N2" s="3" t="n">
         <v>134003.54</v>
       </c>
     </row>
@@ -615,12 +624,15 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>50</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="M3" s="2" t="n">
         <v>31.64</v>
       </c>
-      <c r="M3" s="3" t="n">
+      <c r="N3" s="3" t="n">
         <v>131644.78</v>
       </c>
     </row>
@@ -657,15 +669,18 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
         <v>42.9</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="M4" s="2" t="n">
         <v>28.06</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="N4" s="3" t="n">
         <v>128059.99</v>
       </c>
     </row>
@@ -705,12 +720,15 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>33.3</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="M5" s="2" t="n">
         <v>19.75</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="N5" s="3" t="n">
         <v>119750.4</v>
       </c>
     </row>
@@ -750,12 +768,15 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>50</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="M6" s="2" t="n">
         <v>15.88</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="N6" s="3" t="n">
         <v>115882.11</v>
       </c>
     </row>
@@ -795,12 +816,15 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>50</v>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="M7" s="2" t="n">
         <v>10.06</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="N7" s="3" t="n">
         <v>110063.03</v>
       </c>
     </row>
@@ -840,12 +864,15 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>100</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="M8" s="2" t="n">
         <v>6.35</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="N8" s="3" t="n">
         <v>106347.83</v>
       </c>
     </row>
@@ -885,12 +912,15 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>25</v>
       </c>
-      <c r="L9" s="2" t="n">
+      <c r="M9" s="2" t="n">
         <v>3.87</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="N9" s="3" t="n">
         <v>103865.18</v>
       </c>
     </row>
@@ -930,12 +960,15 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>16.7</v>
       </c>
-      <c r="L10" s="2" t="n">
+      <c r="M10" s="2" t="n">
         <v>2.72</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="N10" s="3" t="n">
         <v>102723.46</v>
       </c>
     </row>
@@ -975,12 +1008,15 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>50</v>
       </c>
-      <c r="L11" s="2" t="n">
+      <c r="M11" s="2" t="n">
         <v>2.59</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="N11" s="3" t="n">
         <v>102591.18</v>
       </c>
     </row>
@@ -1019,10 +1055,13 @@
       <c r="J12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="3" t="n">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -1061,10 +1100,13 @@
       <c r="J13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="3" t="n">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -1103,10 +1145,13 @@
       <c r="J14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="n">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -1145,10 +1190,13 @@
       <c r="J15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3" t="n">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -1187,10 +1235,13 @@
       <c r="J16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="3" t="n">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="3" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -1229,10 +1280,13 @@
       <c r="J17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="3" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -1269,15 +1323,18 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N18" s="3" t="n">
         <v>99000</v>
       </c>
     </row>
@@ -1319,10 +1376,13 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M19" s="3" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N19" s="3" t="n">
         <v>99000</v>
       </c>
     </row>
@@ -1364,10 +1424,13 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M20" s="3" t="n">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N20" s="3" t="n">
         <v>99000</v>
       </c>
     </row>
@@ -1409,10 +1472,13 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M21" s="3" t="n">
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N21" s="3" t="n">
         <v>99000</v>
       </c>
     </row>
@@ -1454,10 +1520,13 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M22" s="3" t="n">
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N22" s="3" t="n">
         <v>99000</v>
       </c>
     </row>
@@ -1499,10 +1568,13 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" s="5" t="n">
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="5" t="n">
         <v>-1.99</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="N23" s="3" t="n">
         <v>98010</v>
       </c>
     </row>
@@ -1544,10 +1616,13 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" s="5" t="n">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="5" t="n">
         <v>-1.99</v>
       </c>
-      <c r="M24" s="3" t="n">
+      <c r="N24" s="3" t="n">
         <v>98010</v>
       </c>
     </row>
@@ -1589,10 +1664,13 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" s="5" t="n">
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="5" t="n">
         <v>-2.97</v>
       </c>
-      <c r="M25" s="3" t="n">
+      <c r="N25" s="3" t="n">
         <v>97029.89999999999</v>
       </c>
     </row>
@@ -1634,10 +1712,13 @@
       <c r="K26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" s="5" t="n">
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="5" t="n">
         <v>-2.97</v>
       </c>
-      <c r="M26" s="3" t="n">
+      <c r="N26" s="3" t="n">
         <v>97029.89999999999</v>
       </c>
     </row>
@@ -1681,12 +1762,15 @@
         <v>0</v>
       </c>
       <c r="K27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="L27" s="7" t="n">
+      <c r="M27" s="7" t="n">
         <v>10.98</v>
       </c>
-      <c r="M27" s="8" t="n">
+      <c r="N27" s="8" t="n">
         <v>110981.01</v>
       </c>
     </row>
@@ -1730,12 +1814,15 @@
         <v>0</v>
       </c>
       <c r="K28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="L28" s="7" t="n">
+      <c r="M28" s="7" t="n">
         <v>8.529999999999999</v>
       </c>
-      <c r="M28" s="8" t="n">
+      <c r="N28" s="8" t="n">
         <v>108533.18</v>
       </c>
     </row>
@@ -1779,12 +1866,15 @@
         <v>0</v>
       </c>
       <c r="K29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="L29" s="7" t="n">
+      <c r="M29" s="7" t="n">
         <v>3.28</v>
       </c>
-      <c r="M29" s="8" t="n">
+      <c r="N29" s="8" t="n">
         <v>103277.04</v>
       </c>
     </row>
@@ -1827,11 +1917,14 @@
       <c r="J30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K30" s="6" t="n"/>
-      <c r="L30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="8" t="n">
+      <c r="K30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="6" t="n"/>
+      <c r="M30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="8" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -1874,11 +1967,14 @@
       <c r="J31" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K31" s="6" t="n"/>
-      <c r="L31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="8" t="n">
+      <c r="K31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="6" t="n"/>
+      <c r="M31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="8" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -1921,11 +2017,14 @@
       <c r="J32" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K32" s="6" t="n"/>
-      <c r="L32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="8" t="n">
+      <c r="K32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="6" t="n"/>
+      <c r="M32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="8" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -1968,11 +2067,14 @@
       <c r="J33" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K33" s="6" t="n"/>
-      <c r="L33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="8" t="n">
+      <c r="K33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="6" t="n"/>
+      <c r="M33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="8" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -2015,11 +2117,14 @@
       <c r="J34" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K34" s="6" t="n"/>
-      <c r="L34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="8" t="n">
+      <c r="K34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="6" t="n"/>
+      <c r="M34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="8" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -2062,11 +2167,14 @@
       <c r="J35" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K35" s="6" t="n"/>
-      <c r="L35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="8" t="n">
+      <c r="K35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="6" t="n"/>
+      <c r="M35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="8" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -2109,11 +2217,14 @@
       <c r="J36" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K36" s="6" t="n"/>
-      <c r="L36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="8" t="n">
+      <c r="K36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="6" t="n"/>
+      <c r="M36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="8" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -2159,17 +2270,20 @@
       <c r="K37" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L37" s="10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M37" s="8" t="n">
+      <c r="L37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N37" s="8" t="n">
         <v>99000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -2188,13 +2302,13 @@
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="6" t="n">
         <v>2</v>
@@ -2203,22 +2317,25 @@
         <v>0</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L38" s="10" t="n">
-        <v>-1.99</v>
-      </c>
-      <c r="M38" s="8" t="n">
-        <v>98010</v>
+      <c r="L38" s="6" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="M38" s="10" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="N38" s="8" t="n">
+        <v>98990.10000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>EURO_STOXX_50_Index</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -2237,7 +2354,7 @@
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>2</v>
@@ -2257,17 +2374,20 @@
       <c r="K39" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="10" t="n">
+      <c r="L39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="10" t="n">
         <v>-1.99</v>
       </c>
-      <c r="M39" s="8" t="n">
+      <c r="N39" s="8" t="n">
         <v>98010</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>United_States_Oil_Fund_LP</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -2286,7 +2406,7 @@
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>2</v>
@@ -2301,15 +2421,18 @@
         <v>0</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="10" t="n">
+      <c r="L40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="10" t="n">
         <v>-1.99</v>
       </c>
-      <c r="M40" s="8" t="n">
+      <c r="N40" s="8" t="n">
         <v>98010</v>
       </c>
     </row>
@@ -2355,10 +2478,13 @@
       <c r="K41" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="10" t="n">
+      <c r="L41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="10" t="n">
         <v>-2.97</v>
       </c>
-      <c r="M41" s="8" t="n">
+      <c r="N41" s="8" t="n">
         <v>97029.89999999999</v>
       </c>
     </row>
@@ -2404,17 +2530,20 @@
       <c r="K42" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="10" t="n">
+      <c r="L42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="10" t="n">
         <v>-4.9</v>
       </c>
-      <c r="M42" s="8" t="n">
+      <c r="N42" s="8" t="n">
         <v>95099</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>slowfix daily (target = the first opposite reversal beyond entry, no 5R cap), starting capital 100,000, risk 1.0%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-23). generated 2026-07-25 00:34 UTC.</t>
+          <t>slowfix daily (target = the first opposite reversal beyond entry, no 5R cap), starting capital 100,000, risk 1.0%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-23); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-25 02:41 UTC.</t>
         </is>
       </c>
     </row>
@@ -6330,6 +6459,14 @@
           <t>2026-04-17</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
       <c r="G69" t="n">
         <v>0.8467</v>
       </c>
@@ -6339,16 +6476,25 @@
       <c r="I69" t="n">
         <v>0.8693</v>
       </c>
+      <c r="J69" t="n">
+        <v>0.8498</v>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>data_end</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>1</v>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N69" t="n">
         <v>98010</v>
       </c>
       <c r="O69" t="n">
-        <v>98010</v>
+        <v>98990.10000000001</v>
       </c>
     </row>
     <row r="70">

--- a/output/slowfix_all_markets_daily.xlsx
+++ b/output/slowfix_all_markets_daily.xlsx
@@ -554,11 +554,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F2" t="n">
         <v>5</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>80</v>
@@ -602,11 +602,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -720,7 +720,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>33.3</v>
@@ -746,11 +746,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
@@ -938,11 +938,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F10" t="n">
         <v>6</v>
@@ -986,11 +986,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -1034,11 +1034,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1079,11 +1079,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1124,11 +1124,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1169,11 +1169,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1259,11 +1259,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1304,11 +1304,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
@@ -1352,11 +1352,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
@@ -1400,11 +1400,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -1448,11 +1448,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -1496,11 +1496,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F23" t="n">
         <v>2</v>
@@ -1592,11 +1592,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F24" t="n">
         <v>2</v>
@@ -1640,11 +1640,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F25" t="n">
         <v>3</v>
@@ -1688,11 +1688,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F26" t="n">
         <v>3</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>slowfix daily (target = the first opposite reversal beyond entry, no 5R cap), starting capital 100,000, risk 1.0%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-23); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-25 02:41 UTC.</t>
+          <t>slowfix daily (target = the first opposite reversal beyond entry, no cap), starting capital 100,000, risk 1.0%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 03:03 UTC.</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O79"/>
+  <dimension ref="A1:O81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3285,58 +3285,41 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-01-14</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
+          <t>2026-07-24</t>
+        </is>
       </c>
       <c r="G13" t="n">
-        <v>5097</v>
+        <v>706</v>
       </c>
       <c r="H13" t="n">
-        <v>5050</v>
+        <v>711.3</v>
       </c>
       <c r="I13" t="n">
-        <v>6300</v>
-      </c>
-      <c r="J13" t="n">
-        <v>5050</v>
+        <v>629</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v>-1</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N13" t="n">
-        <v>100000</v>
+        <v>134003.54</v>
       </c>
       <c r="O13" t="n">
-        <v>99000</v>
+        <v>134003.54</v>
       </c>
     </row>
     <row r="14">
@@ -3346,7 +3329,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -3355,28 +3338,28 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>4082</v>
+        <v>5097</v>
       </c>
       <c r="H14" t="n">
-        <v>3930</v>
+        <v>5050</v>
       </c>
       <c r="I14" t="n">
-        <v>4970</v>
+        <v>6300</v>
       </c>
       <c r="J14" t="n">
-        <v>3930</v>
+        <v>5050</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -3390,10 +3373,10 @@
         <v>-1</v>
       </c>
       <c r="N14" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O14" t="n">
         <v>99000</v>
-      </c>
-      <c r="O14" t="n">
-        <v>98010</v>
       </c>
     </row>
     <row r="15">
@@ -3403,7 +3386,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -3412,28 +3395,28 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G15" t="n">
-        <v>2990</v>
+        <v>4082</v>
       </c>
       <c r="H15" t="n">
-        <v>2951</v>
+        <v>3930</v>
       </c>
       <c r="I15" t="n">
-        <v>4442</v>
+        <v>4970</v>
       </c>
       <c r="J15" t="n">
-        <v>2951</v>
+        <v>3930</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -3447,50 +3430,50 @@
         <v>-1</v>
       </c>
       <c r="N15" t="n">
+        <v>99000</v>
+      </c>
+      <c r="O15" t="n">
         <v>98010</v>
-      </c>
-      <c r="O15" t="n">
-        <v>97029.89999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures</t>
+          <t>Cocoa_NYCSCE_Futures</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>377.8</v>
+        <v>2990</v>
       </c>
       <c r="H16" t="n">
-        <v>382.86</v>
+        <v>2951</v>
       </c>
       <c r="I16" t="n">
-        <v>343.04</v>
+        <v>4442</v>
       </c>
       <c r="J16" t="n">
-        <v>382.86</v>
+        <v>2951</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -3504,10 +3487,10 @@
         <v>-1</v>
       </c>
       <c r="N16" t="n">
-        <v>100000</v>
+        <v>98010</v>
       </c>
       <c r="O16" t="n">
-        <v>99000</v>
+        <v>97029.89999999999</v>
       </c>
     </row>
     <row r="17">
@@ -3517,111 +3500,111 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>345.1</v>
+        <v>377.8</v>
       </c>
       <c r="H17" t="n">
-        <v>341.79</v>
+        <v>382.86</v>
       </c>
       <c r="I17" t="n">
-        <v>377.8</v>
+        <v>343.04</v>
       </c>
       <c r="J17" t="n">
-        <v>359.4</v>
+        <v>382.86</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>bullish_reversal</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.3202</v>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>4.3202</v>
+        <v>-1</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N17" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O17" t="n">
         <v>99000</v>
-      </c>
-      <c r="O17" t="n">
-        <v>103277.04</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures</t>
+          <t>Coffee_NYCSCE_Futures</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
-        <v>478.2</v>
+        <v>345.1</v>
       </c>
       <c r="H18" t="n">
-        <v>480.1</v>
+        <v>341.79</v>
       </c>
       <c r="I18" t="n">
-        <v>448</v>
+        <v>377.8</v>
       </c>
       <c r="J18" t="n">
-        <v>480.1</v>
+        <v>359.4</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>bullish_reversal</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v>-1</v>
+        <v>4.3202</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>4.3202</v>
       </c>
       <c r="N18" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O18" t="n">
-        <v>99000</v>
+        <v>103277.04</v>
       </c>
     </row>
     <row r="19">
@@ -3631,7 +3614,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3640,45 +3623,45 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>486.4</v>
+        <v>478.2</v>
       </c>
       <c r="H19" t="n">
-        <v>487.5</v>
+        <v>480.1</v>
       </c>
       <c r="I19" t="n">
         <v>448</v>
       </c>
       <c r="J19" t="n">
-        <v>462</v>
+        <v>480.1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>bearish_reversal</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>22.1818</v>
-      </c>
-      <c r="M19" s="2" t="n">
-        <v>22.1818</v>
+        <v>-1</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N19" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O19" t="n">
         <v>99000</v>
-      </c>
-      <c r="O19" t="n">
-        <v>120960</v>
       </c>
     </row>
     <row r="20">
@@ -3688,94 +3671,94 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>411</v>
+        <v>486.4</v>
       </c>
       <c r="H20" t="n">
-        <v>408.3</v>
+        <v>487.5</v>
       </c>
       <c r="I20" t="n">
-        <v>463</v>
+        <v>448</v>
       </c>
       <c r="J20" t="n">
-        <v>408.3</v>
+        <v>462</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>bearish_reversal</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v>-1</v>
+        <v>22.1818</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>22.1818</v>
       </c>
       <c r="N20" t="n">
+        <v>99000</v>
+      </c>
+      <c r="O20" t="n">
         <v>120960</v>
-      </c>
-      <c r="O20" t="n">
-        <v>119750.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini</t>
+          <t>Corn_CBOT_Futures</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>49750</v>
+        <v>411</v>
       </c>
       <c r="H21" t="n">
-        <v>49811</v>
+        <v>408.3</v>
       </c>
       <c r="I21" t="n">
-        <v>46171</v>
+        <v>463</v>
       </c>
       <c r="J21" t="n">
-        <v>49811</v>
+        <v>408.3</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3789,20 +3772,20 @@
         <v>-1</v>
       </c>
       <c r="N21" t="n">
-        <v>100000</v>
+        <v>120960</v>
       </c>
       <c r="O21" t="n">
-        <v>99000</v>
+        <v>119750.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini</t>
+          <t>Corn_CBOT_Futures</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3811,45 +3794,28 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>6</v>
+          <t>2026-07-24</t>
+        </is>
       </c>
       <c r="G22" t="n">
-        <v>51744</v>
+        <v>488.1</v>
       </c>
       <c r="H22" t="n">
-        <v>51850</v>
+        <v>492.1</v>
       </c>
       <c r="I22" t="n">
-        <v>49419</v>
-      </c>
-      <c r="J22" t="n">
-        <v>51850</v>
+        <v>458.5</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M22" s="5" t="n">
-        <v>-1</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N22" t="n">
-        <v>99000</v>
+        <v>119750.4</v>
       </c>
       <c r="O22" t="n">
-        <v>98010</v>
+        <v>119750.4</v>
       </c>
     </row>
     <row r="23">
@@ -3859,7 +3825,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3868,28 +3834,28 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>52734</v>
+        <v>49750</v>
       </c>
       <c r="H23" t="n">
-        <v>53106</v>
+        <v>49811</v>
       </c>
       <c r="I23" t="n">
-        <v>50737</v>
+        <v>46171</v>
       </c>
       <c r="J23" t="n">
-        <v>53106</v>
+        <v>49811</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3903,20 +3869,20 @@
         <v>-1</v>
       </c>
       <c r="N23" t="n">
-        <v>98010</v>
+        <v>100000</v>
       </c>
       <c r="O23" t="n">
-        <v>97029.89999999999</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EURO_Futures</t>
+          <t>Dow_Futures_E_mini</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3925,28 +3891,28 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G24" t="n">
-        <v>1.1783</v>
+        <v>51744</v>
       </c>
       <c r="H24" t="n">
-        <v>1.17986</v>
+        <v>51850</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1614</v>
+        <v>49419</v>
       </c>
       <c r="J24" t="n">
-        <v>1.17986</v>
+        <v>51850</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3960,56 +3926,73 @@
         <v>-1</v>
       </c>
       <c r="N24" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O24" t="n">
-        <v>99000</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EURO_Futures</t>
+          <t>Dow_Futures_E_mini</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>1.1391</v>
+        <v>52734</v>
       </c>
       <c r="H25" t="n">
-        <v>1.13634</v>
+        <v>53106</v>
       </c>
       <c r="I25" t="n">
-        <v>1.1664</v>
+        <v>50737</v>
+      </c>
+      <c r="J25" t="n">
+        <v>53106</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M25" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>99000</v>
+        <v>98010</v>
       </c>
       <c r="O25" t="n">
-        <v>99000</v>
+        <v>97029.89999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index</t>
+          <t>EURO_Futures</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -4022,28 +4005,28 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>6043.4</v>
+        <v>1.1783</v>
       </c>
       <c r="H26" t="n">
-        <v>6073.35</v>
+        <v>1.17986</v>
       </c>
       <c r="I26" t="n">
-        <v>5863</v>
+        <v>1.1614</v>
       </c>
       <c r="J26" t="n">
-        <v>6073.35</v>
+        <v>1.17986</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -4066,7 +4049,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index</t>
+          <t>EURO_Futures</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -4074,56 +4057,39 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>4</v>
+          <t>2026-06-24</t>
+        </is>
       </c>
       <c r="G27" t="n">
-        <v>6060.23</v>
+        <v>1.1391</v>
       </c>
       <c r="H27" t="n">
-        <v>6099.08</v>
+        <v>1.13634</v>
       </c>
       <c r="I27" t="n">
-        <v>5916.3</v>
-      </c>
-      <c r="J27" t="n">
-        <v>6099.08</v>
+        <v>1.1664</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M27" s="5" t="n">
-        <v>-1</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N27" t="n">
         <v>99000</v>
       </c>
       <c r="O27" t="n">
-        <v>98010</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance</t>
+          <t>EURO_STOXX_50_Index</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -4131,33 +4097,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>2812</v>
+        <v>6043.4</v>
       </c>
       <c r="H28" t="n">
-        <v>2754</v>
+        <v>6073.35</v>
       </c>
       <c r="I28" t="n">
-        <v>3364</v>
+        <v>5863</v>
       </c>
       <c r="J28" t="n">
-        <v>2754</v>
+        <v>6073.35</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4180,7 +4146,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance</t>
+          <t>EURO_STOXX_50_Index</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -4188,50 +4154,50 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>1818</v>
+        <v>6060.23</v>
       </c>
       <c r="H29" t="n">
-        <v>1799</v>
+        <v>6099.08</v>
       </c>
       <c r="I29" t="n">
-        <v>2022</v>
+        <v>5916.3</v>
       </c>
       <c r="J29" t="n">
-        <v>2022</v>
+        <v>6099.08</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>bullish_reversal</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>10.7368</v>
-      </c>
-      <c r="M29" s="2" t="n">
-        <v>10.7368</v>
+        <v>-1</v>
+      </c>
+      <c r="M29" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N29" t="n">
         <v>99000</v>
       </c>
       <c r="O29" t="n">
-        <v>109629.47</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="30">
@@ -4241,37 +4207,37 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>2370</v>
+        <v>2812</v>
       </c>
       <c r="H30" t="n">
-        <v>2386</v>
+        <v>2754</v>
       </c>
       <c r="I30" t="n">
-        <v>1971</v>
+        <v>3364</v>
       </c>
       <c r="J30" t="n">
-        <v>2386</v>
+        <v>2754</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4285,77 +4251,77 @@
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>109629.47</v>
+        <v>100000</v>
       </c>
       <c r="O30" t="n">
-        <v>108533.18</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>German_Long_Bund</t>
+          <t>Ethereum_Per_USD_Binance</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>127.47</v>
+        <v>1818</v>
       </c>
       <c r="H31" t="n">
-        <v>127.7</v>
+        <v>1799</v>
       </c>
       <c r="I31" t="n">
-        <v>125.6</v>
+        <v>2022</v>
       </c>
       <c r="J31" t="n">
-        <v>126.01</v>
+        <v>2022</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>bearish_reversal</t>
+          <t>bullish_reversal</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>6.3478</v>
+        <v>10.7368</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>6.3478</v>
+        <v>10.7368</v>
       </c>
       <c r="N31" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O31" t="n">
-        <v>106347.83</v>
+        <v>109629.47</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX</t>
+          <t>Ethereum_Per_USD_Binance</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4364,55 +4330,55 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" t="n">
-        <v>4393</v>
+        <v>2370</v>
       </c>
       <c r="H32" t="n">
-        <v>4409.6</v>
+        <v>2386</v>
       </c>
       <c r="I32" t="n">
-        <v>4162</v>
+        <v>1971</v>
       </c>
       <c r="J32" t="n">
-        <v>4202</v>
+        <v>2386</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>bearish_reversal</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>11.506</v>
-      </c>
-      <c r="M32" s="2" t="n">
-        <v>11.506</v>
+        <v>-1</v>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N32" t="n">
-        <v>100000</v>
+        <v>109629.47</v>
       </c>
       <c r="O32" t="n">
-        <v>111506.02</v>
+        <v>108533.18</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX</t>
+          <t>German_Long_Bund</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4421,45 +4387,45 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G33" t="n">
-        <v>4393</v>
+        <v>127.47</v>
       </c>
       <c r="H33" t="n">
-        <v>4420.6</v>
+        <v>127.7</v>
       </c>
       <c r="I33" t="n">
-        <v>4162</v>
+        <v>125.6</v>
       </c>
       <c r="J33" t="n">
-        <v>4420.6</v>
+        <v>126.01</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>bearish_reversal</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M33" s="5" t="n">
-        <v>-1</v>
+        <v>6.3478</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>6.3478</v>
       </c>
       <c r="N33" t="n">
-        <v>111506.02</v>
+        <v>100000</v>
       </c>
       <c r="O33" t="n">
-        <v>110390.96</v>
+        <v>106347.83</v>
       </c>
     </row>
     <row r="34">
@@ -4469,7 +4435,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4478,28 +4444,28 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>5358.1</v>
+        <v>4393</v>
       </c>
       <c r="H34" t="n">
-        <v>5434.2</v>
+        <v>4409.6</v>
       </c>
       <c r="I34" t="n">
-        <v>4900</v>
+        <v>4162</v>
       </c>
       <c r="J34" t="n">
-        <v>5035</v>
+        <v>4202</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4507,16 +4473,16 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4.2457</v>
+        <v>11.506</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>4.2457</v>
+        <v>11.506</v>
       </c>
       <c r="N34" t="n">
-        <v>110390.96</v>
+        <v>100000</v>
       </c>
       <c r="O34" t="n">
-        <v>115077.87</v>
+        <v>111506.02</v>
       </c>
     </row>
     <row r="35">
@@ -4526,54 +4492,54 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="G35" t="n">
-        <v>4335</v>
+        <v>4393</v>
       </c>
       <c r="H35" t="n">
-        <v>4306.2</v>
+        <v>4420.6</v>
       </c>
       <c r="I35" t="n">
-        <v>5210.5</v>
+        <v>4162</v>
       </c>
       <c r="J35" t="n">
-        <v>4758</v>
+        <v>4420.6</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>bullish_reversal</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>14.6875</v>
-      </c>
-      <c r="M35" s="2" t="n">
-        <v>14.6875</v>
+        <v>-1</v>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N35" t="n">
-        <v>115077.87</v>
+        <v>111506.02</v>
       </c>
       <c r="O35" t="n">
-        <v>131979.93</v>
+        <v>110390.96</v>
       </c>
     </row>
     <row r="36">
@@ -4583,54 +4549,54 @@
         </is>
       </c>
       <c r="B36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
         <v>5</v>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>1</v>
-      </c>
       <c r="G36" t="n">
-        <v>4746</v>
+        <v>5358.1</v>
       </c>
       <c r="H36" t="n">
-        <v>4758.5</v>
+        <v>5434.2</v>
       </c>
       <c r="I36" t="n">
-        <v>4500</v>
+        <v>4900</v>
       </c>
       <c r="J36" t="n">
-        <v>4758.5</v>
+        <v>5035</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>bearish_reversal</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M36" s="5" t="n">
-        <v>-1</v>
+        <v>4.2457</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>4.2457</v>
       </c>
       <c r="N36" t="n">
-        <v>131979.93</v>
+        <v>110390.96</v>
       </c>
       <c r="O36" t="n">
-        <v>130660.13</v>
+        <v>115077.87</v>
       </c>
     </row>
     <row r="37">
@@ -4640,7 +4606,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4649,45 +4615,45 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="G37" t="n">
-        <v>4347</v>
+        <v>4335</v>
       </c>
       <c r="H37" t="n">
-        <v>4292.9</v>
+        <v>4306.2</v>
       </c>
       <c r="I37" t="n">
-        <v>4674</v>
+        <v>5210.5</v>
       </c>
       <c r="J37" t="n">
-        <v>4292.9</v>
+        <v>4758</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>bullish_reversal</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M37" s="5" t="n">
-        <v>-1</v>
+        <v>14.6875</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>14.6875</v>
       </c>
       <c r="N37" t="n">
-        <v>130660.13</v>
+        <v>115077.87</v>
       </c>
       <c r="O37" t="n">
-        <v>129353.53</v>
+        <v>131979.93</v>
       </c>
     </row>
     <row r="38">
@@ -4697,37 +4663,37 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>4103</v>
+        <v>4746</v>
       </c>
       <c r="H38" t="n">
-        <v>4046.1</v>
+        <v>4758.5</v>
       </c>
       <c r="I38" t="n">
-        <v>4674</v>
+        <v>4500</v>
       </c>
       <c r="J38" t="n">
-        <v>4046.1</v>
+        <v>4758.5</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -4741,10 +4707,10 @@
         <v>-1</v>
       </c>
       <c r="N38" t="n">
-        <v>129353.53</v>
+        <v>131979.93</v>
       </c>
       <c r="O38" t="n">
-        <v>128059.99</v>
+        <v>130660.13</v>
       </c>
     </row>
     <row r="39">
@@ -4754,7 +4720,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4763,68 +4729,85 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>3984</v>
+        <v>4347</v>
       </c>
       <c r="H39" t="n">
-        <v>3955.3</v>
+        <v>4292.9</v>
       </c>
       <c r="I39" t="n">
-        <v>4544</v>
+        <v>4674</v>
+      </c>
+      <c r="J39" t="n">
+        <v>4292.9</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N39" t="n">
-        <v>128059.99</v>
+        <v>130660.13</v>
       </c>
       <c r="O39" t="n">
-        <v>128059.99</v>
+        <v>129353.53</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G40" t="n">
-        <v>0.006417</v>
+        <v>4103</v>
       </c>
       <c r="H40" t="n">
-        <v>0.006454</v>
+        <v>4046.1</v>
       </c>
       <c r="I40" t="n">
-        <v>0.006254</v>
+        <v>4674</v>
       </c>
       <c r="J40" t="n">
-        <v>0.006454</v>
+        <v>4046.1</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -4838,77 +4821,60 @@
         <v>-1</v>
       </c>
       <c r="N40" t="n">
-        <v>100000</v>
+        <v>129353.53</v>
       </c>
       <c r="O40" t="n">
-        <v>99000</v>
+        <v>128059.99</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>1</v>
+          <t>2026-06-30</t>
+        </is>
       </c>
       <c r="G41" t="n">
-        <v>239.06</v>
+        <v>3984</v>
       </c>
       <c r="H41" t="n">
-        <v>239.73</v>
+        <v>3955.3</v>
       </c>
       <c r="I41" t="n">
-        <v>233</v>
-      </c>
-      <c r="J41" t="n">
-        <v>239.73</v>
+        <v>4544</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M41" s="5" t="n">
-        <v>-1</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N41" t="n">
-        <v>100000</v>
+        <v>128059.99</v>
       </c>
       <c r="O41" t="n">
-        <v>99000</v>
+        <v>128059.99</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME</t>
+          <t>Japanese_Yen_Futures</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4917,45 +4883,45 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G42" t="n">
-        <v>251.58</v>
+        <v>0.006417</v>
       </c>
       <c r="H42" t="n">
-        <v>251.91</v>
+        <v>0.006454</v>
       </c>
       <c r="I42" t="n">
-        <v>241.8</v>
+        <v>0.006254</v>
       </c>
       <c r="J42" t="n">
-        <v>243.04</v>
+        <v>0.006454</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>bearish_reversal</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>25.8788</v>
-      </c>
-      <c r="M42" s="2" t="n">
-        <v>25.8788</v>
+        <v>-1</v>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N42" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O42" t="n">
         <v>99000</v>
-      </c>
-      <c r="O42" t="n">
-        <v>124620</v>
       </c>
     </row>
     <row r="43">
@@ -4965,7 +4931,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4974,45 +4940,45 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>255.38</v>
+        <v>239.06</v>
       </c>
       <c r="H43" t="n">
-        <v>256.63</v>
+        <v>239.73</v>
       </c>
       <c r="I43" t="n">
-        <v>243.04</v>
+        <v>233</v>
       </c>
       <c r="J43" t="n">
-        <v>247</v>
+        <v>239.73</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>bearish_reversal</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>6.704</v>
-      </c>
-      <c r="M43" s="2" t="n">
-        <v>6.704</v>
+        <v>-1</v>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N43" t="n">
-        <v>124620</v>
+        <v>100000</v>
       </c>
       <c r="O43" t="n">
-        <v>132974.52</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="44">
@@ -5022,151 +4988,151 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>2</v>
       </c>
       <c r="G44" t="n">
-        <v>235.2</v>
+        <v>251.58</v>
       </c>
       <c r="H44" t="n">
-        <v>234.36</v>
+        <v>251.91</v>
       </c>
       <c r="I44" t="n">
-        <v>247.6</v>
+        <v>241.8</v>
       </c>
       <c r="J44" t="n">
-        <v>234.36</v>
+        <v>243.04</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>bearish_reversal</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M44" s="5" t="n">
-        <v>-1</v>
+        <v>25.8788</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>25.8788</v>
       </c>
       <c r="N44" t="n">
-        <v>132974.52</v>
+        <v>99000</v>
       </c>
       <c r="O44" t="n">
-        <v>131644.78</v>
+        <v>124620</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>Live_Cattle_Futures_CME</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G45" t="n">
-        <v>5.7714</v>
+        <v>255.38</v>
       </c>
       <c r="H45" t="n">
-        <v>5.6849</v>
+        <v>256.63</v>
       </c>
       <c r="I45" t="n">
-        <v>6.2179</v>
+        <v>243.04</v>
       </c>
       <c r="J45" t="n">
-        <v>5.6849</v>
+        <v>247</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>bearish_reversal</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M45" s="5" t="n">
-        <v>-1</v>
+        <v>6.704</v>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>6.704</v>
       </c>
       <c r="N45" t="n">
-        <v>100000</v>
+        <v>124620</v>
       </c>
       <c r="O45" t="n">
-        <v>99000</v>
+        <v>132974.52</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>Live_Cattle_Futures_CME</t>
         </is>
       </c>
       <c r="B46" t="n">
+        <v>4</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
         <v>2</v>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>1</v>
-      </c>
       <c r="G46" t="n">
-        <v>5.7714</v>
+        <v>235.2</v>
       </c>
       <c r="H46" t="n">
-        <v>5.6774</v>
+        <v>234.36</v>
       </c>
       <c r="I46" t="n">
-        <v>6.116</v>
+        <v>247.6</v>
       </c>
       <c r="J46" t="n">
-        <v>5.6774</v>
+        <v>234.36</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -5180,10 +5146,10 @@
         <v>-1</v>
       </c>
       <c r="N46" t="n">
-        <v>99000</v>
+        <v>132974.52</v>
       </c>
       <c r="O46" t="n">
-        <v>98010</v>
+        <v>131644.78</v>
       </c>
     </row>
     <row r="47">
@@ -5193,7 +5159,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5202,45 +5168,45 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>5.3133</v>
+        <v>5.7714</v>
       </c>
       <c r="H47" t="n">
-        <v>5.2459</v>
+        <v>5.6849</v>
       </c>
       <c r="I47" t="n">
-        <v>6.07</v>
+        <v>6.2179</v>
       </c>
       <c r="J47" t="n">
-        <v>5.7881</v>
+        <v>5.6849</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>bullish_reversal</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>7.0445</v>
-      </c>
-      <c r="M47" s="2" t="n">
-        <v>7.0445</v>
+        <v>-1</v>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N47" t="n">
-        <v>98010</v>
+        <v>100000</v>
       </c>
       <c r="O47" t="n">
-        <v>104914.32</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="48">
@@ -5250,37 +5216,37 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>6.0956</v>
+        <v>5.7714</v>
       </c>
       <c r="H48" t="n">
-        <v>6.1481</v>
+        <v>5.6774</v>
       </c>
       <c r="I48" t="n">
-        <v>5.45</v>
+        <v>6.116</v>
       </c>
       <c r="J48" t="n">
-        <v>6.1481</v>
+        <v>5.6774</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -5294,77 +5260,77 @@
         <v>-1</v>
       </c>
       <c r="N48" t="n">
-        <v>104914.32</v>
+        <v>99000</v>
       </c>
       <c r="O48" t="n">
-        <v>103865.18</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G49" t="n">
-        <v>3.305</v>
+        <v>5.3133</v>
       </c>
       <c r="H49" t="n">
-        <v>3.354</v>
+        <v>5.2459</v>
       </c>
       <c r="I49" t="n">
-        <v>3.095</v>
+        <v>6.07</v>
       </c>
       <c r="J49" t="n">
-        <v>3.354</v>
+        <v>5.7881</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>bullish_reversal</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M49" s="5" t="n">
-        <v>-1</v>
+        <v>7.0445</v>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>7.0445</v>
       </c>
       <c r="N49" t="n">
-        <v>100000</v>
+        <v>98010</v>
       </c>
       <c r="O49" t="n">
-        <v>99000</v>
+        <v>104914.32</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5373,51 +5339,51 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G50" t="n">
-        <v>3.305</v>
+        <v>6.0956</v>
       </c>
       <c r="H50" t="n">
-        <v>3.356</v>
+        <v>6.1481</v>
       </c>
       <c r="I50" t="n">
-        <v>3.12</v>
+        <v>5.45</v>
       </c>
       <c r="J50" t="n">
-        <v>3.12</v>
+        <v>6.1481</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>bearish_reversal</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.6275</v>
-      </c>
-      <c r="M50" s="2" t="n">
-        <v>3.6275</v>
+        <v>-1</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N50" t="n">
-        <v>99000</v>
+        <v>104914.32</v>
       </c>
       <c r="O50" t="n">
-        <v>102591.18</v>
+        <v>103865.18</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -5425,33 +5391,33 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>1360.4</v>
+        <v>3.305</v>
       </c>
       <c r="H51" t="n">
-        <v>1343.4</v>
+        <v>3.354</v>
       </c>
       <c r="I51" t="n">
-        <v>1550</v>
+        <v>3.095</v>
       </c>
       <c r="J51" t="n">
-        <v>1343.4</v>
+        <v>3.354</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -5474,7 +5440,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -5482,56 +5448,56 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>1167</v>
+        <v>3.305</v>
       </c>
       <c r="H52" t="n">
-        <v>1159.4</v>
+        <v>3.356</v>
       </c>
       <c r="I52" t="n">
-        <v>1392</v>
+        <v>3.12</v>
       </c>
       <c r="J52" t="n">
-        <v>1296.6</v>
+        <v>3.12</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>bullish_reversal</t>
+          <t>bearish_reversal</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>17.0526</v>
+        <v>3.6275</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>17.0526</v>
+        <v>3.6275</v>
       </c>
       <c r="N52" t="n">
         <v>99000</v>
       </c>
       <c r="O52" t="n">
-        <v>115882.11</v>
+        <v>102591.18</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -5539,33 +5505,33 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G53" t="n">
-        <v>2084.6</v>
+        <v>1360.4</v>
       </c>
       <c r="H53" t="n">
-        <v>2113.7</v>
+        <v>1343.4</v>
       </c>
       <c r="I53" t="n">
-        <v>1875</v>
+        <v>1550</v>
       </c>
       <c r="J53" t="n">
-        <v>2113.7</v>
+        <v>1343.4</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -5588,7 +5554,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -5601,45 +5567,45 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G54" t="n">
-        <v>1641.5</v>
+        <v>1167</v>
       </c>
       <c r="H54" t="n">
-        <v>1621</v>
+        <v>1159.4</v>
       </c>
       <c r="I54" t="n">
-        <v>1908.5</v>
+        <v>1392</v>
       </c>
       <c r="J54" t="n">
-        <v>1621</v>
+        <v>1296.6</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>bullish_reversal</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M54" s="5" t="n">
-        <v>-1</v>
+        <v>17.0526</v>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>17.0526</v>
       </c>
       <c r="N54" t="n">
         <v>99000</v>
       </c>
       <c r="O54" t="n">
-        <v>98010</v>
+        <v>115882.11</v>
       </c>
     </row>
     <row r="55">
@@ -5649,37 +5615,37 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G55" t="n">
-        <v>1581.5</v>
+        <v>2084.6</v>
       </c>
       <c r="H55" t="n">
-        <v>1547.6</v>
+        <v>2113.7</v>
       </c>
       <c r="I55" t="n">
-        <v>1908.5</v>
+        <v>1875</v>
       </c>
       <c r="J55" t="n">
-        <v>1547.6</v>
+        <v>2113.7</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -5693,50 +5659,50 @@
         <v>-1</v>
       </c>
       <c r="N55" t="n">
-        <v>98010</v>
+        <v>100000</v>
       </c>
       <c r="O55" t="n">
-        <v>97029.89999999999</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>27907</v>
+        <v>1641.5</v>
       </c>
       <c r="H56" t="n">
-        <v>27965.76</v>
+        <v>1621</v>
       </c>
       <c r="I56" t="n">
-        <v>26551.6</v>
+        <v>1908.5</v>
       </c>
       <c r="J56" t="n">
-        <v>27965.76</v>
+        <v>1621</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -5750,50 +5716,50 @@
         <v>-1</v>
       </c>
       <c r="N56" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O56" t="n">
-        <v>99000</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G57" t="n">
-        <v>7206.55</v>
+        <v>1581.5</v>
       </c>
       <c r="H57" t="n">
-        <v>7223.26</v>
+        <v>1547.6</v>
       </c>
       <c r="I57" t="n">
-        <v>6766</v>
+        <v>1908.5</v>
       </c>
       <c r="J57" t="n">
-        <v>7223.26</v>
+        <v>1547.6</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -5807,16 +5773,16 @@
         <v>-1</v>
       </c>
       <c r="N57" t="n">
-        <v>100000</v>
+        <v>98010</v>
       </c>
       <c r="O57" t="n">
-        <v>99000</v>
+        <v>97029.89999999999</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -5829,28 +5795,28 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>6957.43</v>
+        <v>27907</v>
       </c>
       <c r="H58" t="n">
-        <v>6965.7</v>
+        <v>27965.76</v>
       </c>
       <c r="I58" t="n">
-        <v>6806.6</v>
+        <v>26551.6</v>
       </c>
       <c r="J58" t="n">
-        <v>6965.7</v>
+        <v>27965.76</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5873,41 +5839,41 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
         <v>2</v>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>1</v>
-      </c>
       <c r="G59" t="n">
-        <v>6982.4</v>
+        <v>7206.55</v>
       </c>
       <c r="H59" t="n">
-        <v>6988.83</v>
+        <v>7223.26</v>
       </c>
       <c r="I59" t="n">
-        <v>6792.5</v>
+        <v>6766</v>
       </c>
       <c r="J59" t="n">
-        <v>6988.83</v>
+        <v>7223.26</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5921,10 +5887,10 @@
         <v>-1</v>
       </c>
       <c r="N59" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O59" t="n">
         <v>99000</v>
-      </c>
-      <c r="O59" t="n">
-        <v>98010</v>
       </c>
     </row>
     <row r="60">
@@ -5934,7 +5900,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -5943,28 +5909,28 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G60" t="n">
-        <v>6982.4</v>
+        <v>6957.43</v>
       </c>
       <c r="H60" t="n">
-        <v>6992.85</v>
+        <v>6965.7</v>
       </c>
       <c r="I60" t="n">
-        <v>6792.5</v>
+        <v>6806.6</v>
       </c>
       <c r="J60" t="n">
-        <v>6992.85</v>
+        <v>6965.7</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5978,10 +5944,10 @@
         <v>-1</v>
       </c>
       <c r="N60" t="n">
-        <v>98010</v>
+        <v>100000</v>
       </c>
       <c r="O60" t="n">
-        <v>97029.89999999999</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="61">
@@ -5991,7 +5957,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6000,12 +5966,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -6015,13 +5981,13 @@
         <v>6982.4</v>
       </c>
       <c r="H61" t="n">
-        <v>6986.84</v>
+        <v>6988.83</v>
       </c>
       <c r="I61" t="n">
         <v>6792.5</v>
       </c>
       <c r="J61" t="n">
-        <v>6986.84</v>
+        <v>6988.83</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -6035,10 +6001,10 @@
         <v>-1</v>
       </c>
       <c r="N61" t="n">
-        <v>97029.89999999999</v>
+        <v>99000</v>
       </c>
       <c r="O61" t="n">
-        <v>96059.60000000001</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="62">
@@ -6048,37 +6014,37 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G62" t="n">
-        <v>6794.4</v>
+        <v>6982.4</v>
       </c>
       <c r="H62" t="n">
-        <v>6770.77</v>
+        <v>6992.85</v>
       </c>
       <c r="I62" t="n">
-        <v>6964.1</v>
+        <v>6792.5</v>
       </c>
       <c r="J62" t="n">
-        <v>6770.77</v>
+        <v>6992.85</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -6092,20 +6058,20 @@
         <v>-1</v>
       </c>
       <c r="N62" t="n">
-        <v>96059.60000000001</v>
+        <v>98010</v>
       </c>
       <c r="O62" t="n">
-        <v>95099</v>
+        <v>97029.89999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6114,28 +6080,28 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>86.081</v>
+        <v>6982.4</v>
       </c>
       <c r="H63" t="n">
-        <v>88.001</v>
+        <v>6986.84</v>
       </c>
       <c r="I63" t="n">
-        <v>72.434</v>
+        <v>6792.5</v>
       </c>
       <c r="J63" t="n">
-        <v>88.001</v>
+        <v>6986.84</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -6149,20 +6115,20 @@
         <v>-1</v>
       </c>
       <c r="N63" t="n">
-        <v>100000</v>
+        <v>97029.89999999999</v>
       </c>
       <c r="O63" t="n">
-        <v>99000</v>
+        <v>96059.60000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -6171,28 +6137,28 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>73.84399999999999</v>
+        <v>6794.4</v>
       </c>
       <c r="H64" t="n">
-        <v>71.999</v>
+        <v>6770.77</v>
       </c>
       <c r="I64" t="n">
-        <v>89</v>
+        <v>6964.1</v>
       </c>
       <c r="J64" t="n">
-        <v>71.999</v>
+        <v>6770.77</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -6206,16 +6172,16 @@
         <v>-1</v>
       </c>
       <c r="N64" t="n">
-        <v>99000</v>
+        <v>96059.60000000001</v>
       </c>
       <c r="O64" t="n">
-        <v>98010</v>
+        <v>95099</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -6228,28 +6194,28 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>15</v>
+        <v>86.081</v>
       </c>
       <c r="H65" t="n">
-        <v>15.26</v>
+        <v>88.001</v>
       </c>
       <c r="I65" t="n">
-        <v>13.6</v>
+        <v>72.434</v>
       </c>
       <c r="J65" t="n">
-        <v>15.26</v>
+        <v>88.001</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -6272,41 +6238,41 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G66" t="n">
-        <v>20.89</v>
+        <v>73.84399999999999</v>
       </c>
       <c r="H66" t="n">
-        <v>21.07</v>
+        <v>71.999</v>
       </c>
       <c r="I66" t="n">
-        <v>19.9</v>
+        <v>89</v>
       </c>
       <c r="J66" t="n">
-        <v>21.07</v>
+        <v>71.999</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -6320,16 +6286,16 @@
         <v>-1</v>
       </c>
       <c r="N66" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O66" t="n">
-        <v>99000</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -6342,28 +6308,28 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G67" t="n">
-        <v>0.8614000000000001</v>
+        <v>15</v>
       </c>
       <c r="H67" t="n">
-        <v>0.8637</v>
+        <v>15.26</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8418</v>
+        <v>13.6</v>
       </c>
       <c r="J67" t="n">
-        <v>0.8637</v>
+        <v>15.26</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -6386,11 +6352,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Teucrium_Wheat_Fund</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -6399,28 +6365,28 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0.8614000000000001</v>
+        <v>20.89</v>
       </c>
       <c r="H68" t="n">
-        <v>0.8658</v>
+        <v>21.07</v>
       </c>
       <c r="I68" t="n">
-        <v>0.8418</v>
+        <v>19.9</v>
       </c>
       <c r="J68" t="n">
-        <v>0.8658</v>
+        <v>21.07</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -6434,10 +6400,10 @@
         <v>-1</v>
       </c>
       <c r="N68" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O68" t="n">
         <v>99000</v>
-      </c>
-      <c r="O68" t="n">
-        <v>98010</v>
       </c>
     </row>
     <row r="69">
@@ -6447,64 +6413,64 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>0.8467</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>0.8436</v>
+        <v>0.8637</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8693</v>
+        <v>0.8418</v>
       </c>
       <c r="J69" t="n">
-        <v>0.8498</v>
+        <v>0.8637</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>data_end</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1</v>
-      </c>
-      <c r="M69" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
+      </c>
+      <c r="M69" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N69" t="n">
-        <v>98010</v>
+        <v>100000</v>
       </c>
       <c r="O69" t="n">
-        <v>98990.10000000001</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -6513,28 +6479,28 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>116.5</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H70" t="n">
-        <v>116.79</v>
+        <v>0.8658</v>
       </c>
       <c r="I70" t="n">
-        <v>113.7</v>
+        <v>0.8418</v>
       </c>
       <c r="J70" t="n">
-        <v>116.79</v>
+        <v>0.8658</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -6548,73 +6514,73 @@
         <v>-1</v>
       </c>
       <c r="N70" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O70" t="n">
-        <v>99000</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>118.02</v>
+        <v>0.8467</v>
       </c>
       <c r="H71" t="n">
-        <v>118.16</v>
+        <v>0.8436</v>
       </c>
       <c r="I71" t="n">
-        <v>114.7</v>
+        <v>0.8693</v>
       </c>
       <c r="J71" t="n">
-        <v>118.16</v>
+        <v>0.8498</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>data_end</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M71" s="5" t="n">
-        <v>-1</v>
+        <v>1</v>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N71" t="n">
-        <v>99000</v>
+        <v>98010</v>
       </c>
       <c r="O71" t="n">
-        <v>98010</v>
+        <v>98990.10000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -6622,33 +6588,33 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>97.81399999999999</v>
+        <v>116.5</v>
       </c>
       <c r="H72" t="n">
-        <v>97.569</v>
+        <v>116.79</v>
       </c>
       <c r="I72" t="n">
-        <v>98.976</v>
+        <v>113.7</v>
       </c>
       <c r="J72" t="n">
-        <v>97.569</v>
+        <v>116.79</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6671,7 +6637,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -6684,28 +6650,28 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G73" t="n">
-        <v>99.376</v>
+        <v>118.02</v>
       </c>
       <c r="H73" t="n">
-        <v>99.571</v>
+        <v>118.16</v>
       </c>
       <c r="I73" t="n">
-        <v>97.714</v>
+        <v>114.7</v>
       </c>
       <c r="J73" t="n">
-        <v>99.571</v>
+        <v>118.16</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -6732,37 +6698,37 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F74" t="n">
         <v>3</v>
       </c>
       <c r="G74" t="n">
-        <v>100.066</v>
+        <v>97.81399999999999</v>
       </c>
       <c r="H74" t="n">
-        <v>100.201</v>
+        <v>97.569</v>
       </c>
       <c r="I74" t="n">
-        <v>98.31399999999999</v>
+        <v>98.976</v>
       </c>
       <c r="J74" t="n">
-        <v>100.201</v>
+        <v>97.569</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -6776,10 +6742,10 @@
         <v>-1</v>
       </c>
       <c r="N74" t="n">
-        <v>98010</v>
+        <v>100000</v>
       </c>
       <c r="O74" t="n">
-        <v>97029.89999999999</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="75">
@@ -6789,7 +6755,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -6798,28 +6764,28 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G75" t="n">
-        <v>100.066</v>
+        <v>99.376</v>
       </c>
       <c r="H75" t="n">
-        <v>100.361</v>
+        <v>99.571</v>
       </c>
       <c r="I75" t="n">
-        <v>99.004</v>
+        <v>97.714</v>
       </c>
       <c r="J75" t="n">
-        <v>100.361</v>
+        <v>99.571</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6833,10 +6799,10 @@
         <v>-1</v>
       </c>
       <c r="N75" t="n">
-        <v>97029.89999999999</v>
+        <v>99000</v>
       </c>
       <c r="O75" t="n">
-        <v>96059.60000000001</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="76">
@@ -6846,7 +6812,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -6855,28 +6821,28 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G76" t="n">
-        <v>100.621</v>
+        <v>100.066</v>
       </c>
       <c r="H76" t="n">
-        <v>100.911</v>
+        <v>100.201</v>
       </c>
       <c r="I76" t="n">
-        <v>99.004</v>
+        <v>98.31399999999999</v>
       </c>
       <c r="J76" t="n">
-        <v>100.911</v>
+        <v>100.201</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6890,10 +6856,10 @@
         <v>-1</v>
       </c>
       <c r="N76" t="n">
-        <v>96059.60000000001</v>
+        <v>98010</v>
       </c>
       <c r="O76" t="n">
-        <v>95099</v>
+        <v>97029.89999999999</v>
       </c>
     </row>
     <row r="77">
@@ -6903,7 +6869,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -6912,55 +6878,55 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>101.411</v>
+        <v>100.066</v>
       </c>
       <c r="H77" t="n">
-        <v>101.526</v>
+        <v>100.361</v>
       </c>
       <c r="I77" t="n">
         <v>99.004</v>
       </c>
       <c r="J77" t="n">
-        <v>100.489</v>
+        <v>100.361</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>bearish_reversal</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>8.0174</v>
-      </c>
-      <c r="M77" s="2" t="n">
-        <v>8.0174</v>
+        <v>-1</v>
+      </c>
+      <c r="M77" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N77" t="n">
-        <v>95099</v>
+        <v>97029.89999999999</v>
       </c>
       <c r="O77" t="n">
-        <v>102723.46</v>
+        <v>96059.60000000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -6969,28 +6935,28 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G78" t="n">
-        <v>121.72</v>
+        <v>100.621</v>
       </c>
       <c r="H78" t="n">
-        <v>123.03</v>
+        <v>100.911</v>
       </c>
       <c r="I78" t="n">
-        <v>87.2</v>
+        <v>99.004</v>
       </c>
       <c r="J78" t="n">
-        <v>123.03</v>
+        <v>100.911</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -7004,66 +6970,180 @@
         <v>-1</v>
       </c>
       <c r="N78" t="n">
-        <v>100000</v>
+        <v>96059.60000000001</v>
       </c>
       <c r="O78" t="n">
-        <v>99000</v>
+        <v>95099</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>6</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>5</v>
+      </c>
+      <c r="G79" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H79" t="n">
+        <v>101.526</v>
+      </c>
+      <c r="I79" t="n">
+        <v>99.004</v>
+      </c>
+      <c r="J79" t="n">
+        <v>100.489</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>bearish_reversal</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>8.0174</v>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>8.0174</v>
+      </c>
+      <c r="N79" t="n">
+        <v>95099</v>
+      </c>
+      <c r="O79" t="n">
+        <v>102723.46</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>United_States_Oil_Fund_LP</t>
         </is>
       </c>
-      <c r="B79" t="n">
+      <c r="B80" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>5</v>
+      </c>
+      <c r="G80" t="n">
+        <v>121.72</v>
+      </c>
+      <c r="H80" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="I80" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="J80" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M80" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N80" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O80" t="n">
+        <v>99000</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>United_States_Oil_Fund_LP</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
         <v>2</v>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>short</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="F79" t="n">
+      <c r="F81" t="n">
         <v>2</v>
       </c>
-      <c r="G79" t="n">
+      <c r="G81" t="n">
         <v>130.16</v>
       </c>
-      <c r="H79" t="n">
+      <c r="H81" t="n">
         <v>130.94</v>
       </c>
-      <c r="I79" t="n">
+      <c r="I81" t="n">
         <v>98.3</v>
       </c>
-      <c r="J79" t="n">
+      <c r="J81" t="n">
         <v>130.94</v>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>stop</t>
         </is>
       </c>
-      <c r="L79" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M79" s="5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N79" t="n">
+      <c r="L81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M81" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N81" t="n">
         <v>99000</v>
       </c>
-      <c r="O79" t="n">
+      <c r="O81" t="n">
         <v>98010</v>
       </c>
     </row>

--- a/output/slowfix_all_markets_daily.xlsx
+++ b/output/slowfix_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>slowfix daily (target = the first opposite reversal beyond entry, no cap), starting capital 100,000, risk 1.0%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 03:03 UTC.</t>
+          <t>slowfix daily (target = the first opposite reversal beyond entry, no cap), starting capital 100,000, risk 1.0%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 04:17 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/slowfix_all_markets_daily.xlsx
+++ b/output/slowfix_all_markets_daily.xlsx
@@ -582,10 +582,10 @@
         <v>80</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>34</v>
+        <v>56.81</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>134003.54</v>
+        <v>156805.15</v>
       </c>
     </row>
     <row r="3">
@@ -630,10 +630,10 @@
         <v>50</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>31.64</v>
+        <v>50.69</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>131644.78</v>
+        <v>150690.5</v>
       </c>
     </row>
     <row r="4">
@@ -678,10 +678,10 @@
         <v>42.9</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>28.06</v>
+        <v>45.56</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>128059.99</v>
+        <v>145562.78</v>
       </c>
     </row>
     <row r="5">
@@ -726,10 +726,10 @@
         <v>33.3</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>19.75</v>
+        <v>30.68</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>119750.4</v>
+        <v>130681.67</v>
       </c>
     </row>
     <row r="6">
@@ -774,10 +774,10 @@
         <v>50</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>15.88</v>
+        <v>24.83</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>115882.11</v>
+        <v>124828.85</v>
       </c>
     </row>
     <row r="7">
@@ -822,10 +822,10 @@
         <v>50</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>10.06</v>
+        <v>15.73</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>110063.03</v>
+        <v>115728.42</v>
       </c>
     </row>
     <row r="8">
@@ -870,10 +870,10 @@
         <v>100</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6.35</v>
+        <v>9.99</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>106347.83</v>
+        <v>109985.13</v>
       </c>
     </row>
     <row r="9">
@@ -918,16 +918,16 @@
         <v>25</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3.87</v>
+        <v>5.92</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>103865.18</v>
+        <v>105921.12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -942,16 +942,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -963,19 +963,19 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2.72</v>
+        <v>4.04</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>102723.46</v>
+        <v>104043.23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -990,16 +990,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1011,13 +1011,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>50</v>
+        <v>16.7</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2.59</v>
+        <v>4.03</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>102591.18</v>
+        <v>104028.76</v>
       </c>
     </row>
     <row r="12">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>-1</v>
+        <v>-1.57</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="19">
@@ -1380,10 +1380,10 @@
         <v>0</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>-1</v>
+        <v>-1.57</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="20">
@@ -1428,10 +1428,10 @@
         <v>0</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>-1</v>
+        <v>-1.57</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="21">
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>-1</v>
+        <v>-1.57</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="22">
@@ -1524,10 +1524,10 @@
         <v>0</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>-1</v>
+        <v>-1.57</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="23">
@@ -1572,10 +1572,10 @@
         <v>0</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>-1.99</v>
+        <v>-3.12</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>98010</v>
+        <v>96878.74000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1620,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>-1.99</v>
+        <v>-3.12</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>98010</v>
+        <v>96878.74000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1668,10 +1668,10 @@
         <v>0</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>-2.97</v>
+        <v>-4.65</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>97029.89999999999</v>
+        <v>95354.84</v>
       </c>
     </row>
     <row r="26">
@@ -1716,10 +1716,10 @@
         <v>0</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>-2.97</v>
+        <v>-4.65</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>97029.89999999999</v>
+        <v>95354.84</v>
       </c>
     </row>
     <row r="27">
@@ -1768,10 +1768,10 @@
         <v>50</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>10.98</v>
+        <v>17.27</v>
       </c>
       <c r="N27" s="8" t="n">
-        <v>110981.01</v>
+        <v>117266.5</v>
       </c>
     </row>
     <row r="28">
@@ -1820,10 +1820,10 @@
         <v>33.3</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>8.529999999999999</v>
+        <v>13.24</v>
       </c>
       <c r="N28" s="8" t="n">
-        <v>108533.18</v>
+        <v>113240.65</v>
       </c>
     </row>
     <row r="29">
@@ -1872,10 +1872,10 @@
         <v>50</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>3.28</v>
+        <v>5.12</v>
       </c>
       <c r="N29" s="8" t="n">
-        <v>103277.04</v>
+        <v>105115.84</v>
       </c>
     </row>
     <row r="30">
@@ -2274,10 +2274,10 @@
         <v>0</v>
       </c>
       <c r="M37" s="10" t="n">
-        <v>-1</v>
+        <v>-1.57</v>
       </c>
       <c r="N37" s="8" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="38">
@@ -2326,10 +2326,10 @@
         <v>33.3</v>
       </c>
       <c r="M38" s="10" t="n">
-        <v>-1.01</v>
+        <v>-1.6</v>
       </c>
       <c r="N38" s="8" t="n">
-        <v>98990.10000000001</v>
+        <v>98402.64999999999</v>
       </c>
     </row>
     <row r="39">
@@ -2378,10 +2378,10 @@
         <v>0</v>
       </c>
       <c r="M39" s="10" t="n">
-        <v>-1.99</v>
+        <v>-3.12</v>
       </c>
       <c r="N39" s="8" t="n">
-        <v>98010</v>
+        <v>96878.74000000001</v>
       </c>
     </row>
     <row r="40">
@@ -2430,10 +2430,10 @@
         <v>0</v>
       </c>
       <c r="M40" s="10" t="n">
-        <v>-1.99</v>
+        <v>-3.12</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>98010</v>
+        <v>96878.74000000001</v>
       </c>
     </row>
     <row r="41">
@@ -2482,10 +2482,10 @@
         <v>0</v>
       </c>
       <c r="M41" s="10" t="n">
-        <v>-2.97</v>
+        <v>-4.65</v>
       </c>
       <c r="N41" s="8" t="n">
-        <v>97029.89999999999</v>
+        <v>95354.84</v>
       </c>
     </row>
     <row r="42">
@@ -2534,16 +2534,16 @@
         <v>0</v>
       </c>
       <c r="M42" s="10" t="n">
-        <v>-4.9</v>
+        <v>-7.62</v>
       </c>
       <c r="N42" s="8" t="n">
-        <v>95099</v>
+        <v>92378.57000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>slowfix daily (target = the first opposite reversal beyond entry, no cap), starting capital 100,000, risk 1.0%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 04:17 UTC.</t>
+          <t>slowfix daily (target = the first opposite reversal beyond entry, no cap), starting capital 100,000, risk 1.573%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 06:17 UTC.</t>
         </is>
       </c>
     </row>
@@ -2703,13 +2703,13 @@
         <v>-1</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N2" t="n">
         <v>100000</v>
       </c>
       <c r="O2" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="3">
@@ -2760,13 +2760,13 @@
         <v>2.3732</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2.3732</v>
+        <v>3.7331</v>
       </c>
       <c r="N3" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
       <c r="O3" t="n">
-        <v>101349.51</v>
+        <v>102101.38</v>
       </c>
     </row>
     <row r="4">
@@ -2817,13 +2817,13 @@
         <v>10.6094</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>10.6094</v>
+        <v>16.6885</v>
       </c>
       <c r="N4" t="n">
-        <v>101349.51</v>
+        <v>102101.38</v>
       </c>
       <c r="O4" t="n">
-        <v>112102.03</v>
+        <v>119140.58</v>
       </c>
     </row>
     <row r="5">
@@ -2874,13 +2874,13 @@
         <v>-1</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N5" t="n">
-        <v>112102.03</v>
+        <v>119140.58</v>
       </c>
       <c r="O5" t="n">
-        <v>110981.01</v>
+        <v>117266.5</v>
       </c>
     </row>
     <row r="6">
@@ -2931,13 +2931,13 @@
         <v>-1</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N6" t="n">
         <v>100000</v>
       </c>
       <c r="O6" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="7">
@@ -2988,13 +2988,13 @@
         <v>11.1748</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>11.1748</v>
+        <v>17.5779</v>
       </c>
       <c r="N7" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
       <c r="O7" t="n">
-        <v>110063.03</v>
+        <v>115728.42</v>
       </c>
     </row>
     <row r="8">
@@ -3045,13 +3045,13 @@
         <v>6.2472</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6.2472</v>
+        <v>9.8268</v>
       </c>
       <c r="N8" t="n">
         <v>100000</v>
       </c>
       <c r="O8" t="n">
-        <v>106247.19</v>
+        <v>109826.83</v>
       </c>
     </row>
     <row r="9">
@@ -3102,13 +3102,13 @@
         <v>10.137</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>10.137</v>
+        <v>15.9455</v>
       </c>
       <c r="N9" t="n">
-        <v>106247.19</v>
+        <v>109826.83</v>
       </c>
       <c r="O9" t="n">
-        <v>117017.45</v>
+        <v>127339.25</v>
       </c>
     </row>
     <row r="10">
@@ -3159,13 +3159,13 @@
         <v>4.9242</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>4.9242</v>
+        <v>7.7458</v>
       </c>
       <c r="N10" t="n">
-        <v>117017.45</v>
+        <v>127339.25</v>
       </c>
       <c r="O10" t="n">
-        <v>122779.68</v>
+        <v>137202.73</v>
       </c>
     </row>
     <row r="11">
@@ -3216,13 +3216,13 @@
         <v>10.2439</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>10.2439</v>
+        <v>16.1137</v>
       </c>
       <c r="N11" t="n">
-        <v>122779.68</v>
+        <v>137202.73</v>
       </c>
       <c r="O11" t="n">
-        <v>135357.11</v>
+        <v>159311.11</v>
       </c>
     </row>
     <row r="12">
@@ -3273,13 +3273,13 @@
         <v>-1</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N12" t="n">
-        <v>135357.11</v>
+        <v>159311.11</v>
       </c>
       <c r="O12" t="n">
-        <v>134003.54</v>
+        <v>156805.15</v>
       </c>
     </row>
     <row r="13">
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>134003.54</v>
+        <v>156805.15</v>
       </c>
       <c r="O13" t="n">
-        <v>134003.54</v>
+        <v>156805.15</v>
       </c>
     </row>
     <row r="14">
@@ -3370,13 +3370,13 @@
         <v>-1</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N14" t="n">
         <v>100000</v>
       </c>
       <c r="O14" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="15">
@@ -3427,13 +3427,13 @@
         <v>-1</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N15" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
       <c r="O15" t="n">
-        <v>98010</v>
+        <v>96878.74000000001</v>
       </c>
     </row>
     <row r="16">
@@ -3484,13 +3484,13 @@
         <v>-1</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N16" t="n">
-        <v>98010</v>
+        <v>96878.74000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>97029.89999999999</v>
+        <v>95354.84</v>
       </c>
     </row>
     <row r="17">
@@ -3541,13 +3541,13 @@
         <v>-1</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N17" t="n">
         <v>100000</v>
       </c>
       <c r="O17" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="18">
@@ -3598,13 +3598,13 @@
         <v>4.3202</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>4.3202</v>
+        <v>6.7957</v>
       </c>
       <c r="N18" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
       <c r="O18" t="n">
-        <v>103277.04</v>
+        <v>105115.84</v>
       </c>
     </row>
     <row r="19">
@@ -3655,13 +3655,13 @@
         <v>-1</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N19" t="n">
         <v>100000</v>
       </c>
       <c r="O19" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="20">
@@ -3712,13 +3712,13 @@
         <v>22.1818</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>22.1818</v>
+        <v>34.892</v>
       </c>
       <c r="N20" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
       <c r="O20" t="n">
-        <v>120960</v>
+        <v>132770.15</v>
       </c>
     </row>
     <row r="21">
@@ -3769,13 +3769,13 @@
         <v>-1</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N21" t="n">
-        <v>120960</v>
+        <v>132770.15</v>
       </c>
       <c r="O21" t="n">
-        <v>119750.4</v>
+        <v>130681.67</v>
       </c>
     </row>
     <row r="22">
@@ -3812,10 +3812,10 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>119750.4</v>
+        <v>130681.67</v>
       </c>
       <c r="O22" t="n">
-        <v>119750.4</v>
+        <v>130681.67</v>
       </c>
     </row>
     <row r="23">
@@ -3866,13 +3866,13 @@
         <v>-1</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N23" t="n">
         <v>100000</v>
       </c>
       <c r="O23" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="24">
@@ -3923,13 +3923,13 @@
         <v>-1</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N24" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
       <c r="O24" t="n">
-        <v>98010</v>
+        <v>96878.74000000001</v>
       </c>
     </row>
     <row r="25">
@@ -3980,13 +3980,13 @@
         <v>-1</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N25" t="n">
-        <v>98010</v>
+        <v>96878.74000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>97029.89999999999</v>
+        <v>95354.84</v>
       </c>
     </row>
     <row r="26">
@@ -4037,13 +4037,13 @@
         <v>-1</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N26" t="n">
         <v>100000</v>
       </c>
       <c r="O26" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="27">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
       <c r="O27" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="28">
@@ -4134,13 +4134,13 @@
         <v>-1</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N28" t="n">
         <v>100000</v>
       </c>
       <c r="O28" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="29">
@@ -4191,13 +4191,13 @@
         <v>-1</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N29" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
       <c r="O29" t="n">
-        <v>98010</v>
+        <v>96878.74000000001</v>
       </c>
     </row>
     <row r="30">
@@ -4248,13 +4248,13 @@
         <v>-1</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N30" t="n">
         <v>100000</v>
       </c>
       <c r="O30" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="31">
@@ -4305,13 +4305,13 @@
         <v>10.7368</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>10.7368</v>
+        <v>16.8891</v>
       </c>
       <c r="N31" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
       <c r="O31" t="n">
-        <v>109629.47</v>
+        <v>115050.39</v>
       </c>
     </row>
     <row r="32">
@@ -4362,13 +4362,13 @@
         <v>-1</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N32" t="n">
-        <v>109629.47</v>
+        <v>115050.39</v>
       </c>
       <c r="O32" t="n">
-        <v>108533.18</v>
+        <v>113240.65</v>
       </c>
     </row>
     <row r="33">
@@ -4419,13 +4419,13 @@
         <v>6.3478</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>6.3478</v>
+        <v>9.985099999999999</v>
       </c>
       <c r="N33" t="n">
         <v>100000</v>
       </c>
       <c r="O33" t="n">
-        <v>106347.83</v>
+        <v>109985.13</v>
       </c>
     </row>
     <row r="34">
@@ -4476,13 +4476,13 @@
         <v>11.506</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>11.506</v>
+        <v>18.099</v>
       </c>
       <c r="N34" t="n">
         <v>100000</v>
       </c>
       <c r="O34" t="n">
-        <v>111506.02</v>
+        <v>118098.98</v>
       </c>
     </row>
     <row r="35">
@@ -4533,13 +4533,13 @@
         <v>-1</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N35" t="n">
-        <v>111506.02</v>
+        <v>118098.98</v>
       </c>
       <c r="O35" t="n">
-        <v>110390.96</v>
+        <v>116241.28</v>
       </c>
     </row>
     <row r="36">
@@ -4590,13 +4590,13 @@
         <v>4.2457</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4.2457</v>
+        <v>6.6785</v>
       </c>
       <c r="N36" t="n">
-        <v>110390.96</v>
+        <v>116241.28</v>
       </c>
       <c r="O36" t="n">
-        <v>115077.87</v>
+        <v>124004.49</v>
       </c>
     </row>
     <row r="37">
@@ -4647,13 +4647,13 @@
         <v>14.6875</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>14.6875</v>
+        <v>23.1034</v>
       </c>
       <c r="N37" t="n">
-        <v>115077.87</v>
+        <v>124004.49</v>
       </c>
       <c r="O37" t="n">
-        <v>131979.93</v>
+        <v>152653.79</v>
       </c>
     </row>
     <row r="38">
@@ -4704,13 +4704,13 @@
         <v>-1</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N38" t="n">
-        <v>131979.93</v>
+        <v>152653.79</v>
       </c>
       <c r="O38" t="n">
-        <v>130660.13</v>
+        <v>150252.55</v>
       </c>
     </row>
     <row r="39">
@@ -4761,13 +4761,13 @@
         <v>-1</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N39" t="n">
-        <v>130660.13</v>
+        <v>150252.55</v>
       </c>
       <c r="O39" t="n">
-        <v>129353.53</v>
+        <v>147889.07</v>
       </c>
     </row>
     <row r="40">
@@ -4818,13 +4818,13 @@
         <v>-1</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N40" t="n">
-        <v>129353.53</v>
+        <v>147889.07</v>
       </c>
       <c r="O40" t="n">
-        <v>128059.99</v>
+        <v>145562.78</v>
       </c>
     </row>
     <row r="41">
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>128059.99</v>
+        <v>145562.78</v>
       </c>
       <c r="O41" t="n">
-        <v>128059.99</v>
+        <v>145562.78</v>
       </c>
     </row>
     <row r="42">
@@ -4915,13 +4915,13 @@
         <v>-1</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N42" t="n">
         <v>100000</v>
       </c>
       <c r="O42" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="43">
@@ -4972,13 +4972,13 @@
         <v>-1</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N43" t="n">
         <v>100000</v>
       </c>
       <c r="O43" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="44">
@@ -5029,13 +5029,13 @@
         <v>25.8788</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>25.8788</v>
+        <v>40.7073</v>
       </c>
       <c r="N44" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
       <c r="O44" t="n">
-        <v>124620</v>
+        <v>138494.01</v>
       </c>
     </row>
     <row r="45">
@@ -5086,13 +5086,13 @@
         <v>6.704</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>6.704</v>
+        <v>10.5454</v>
       </c>
       <c r="N45" t="n">
-        <v>124620</v>
+        <v>138494.01</v>
       </c>
       <c r="O45" t="n">
-        <v>132974.52</v>
+        <v>153098.74</v>
       </c>
     </row>
     <row r="46">
@@ -5143,13 +5143,13 @@
         <v>-1</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N46" t="n">
-        <v>132974.52</v>
+        <v>153098.74</v>
       </c>
       <c r="O46" t="n">
-        <v>131644.78</v>
+        <v>150690.5</v>
       </c>
     </row>
     <row r="47">
@@ -5200,13 +5200,13 @@
         <v>-1</v>
       </c>
       <c r="M47" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N47" t="n">
         <v>100000</v>
       </c>
       <c r="O47" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="48">
@@ -5257,13 +5257,13 @@
         <v>-1</v>
       </c>
       <c r="M48" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N48" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
       <c r="O48" t="n">
-        <v>98010</v>
+        <v>96878.74000000001</v>
       </c>
     </row>
     <row r="49">
@@ -5314,13 +5314,13 @@
         <v>7.0445</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>7.0445</v>
+        <v>11.081</v>
       </c>
       <c r="N49" t="n">
-        <v>98010</v>
+        <v>96878.74000000001</v>
       </c>
       <c r="O49" t="n">
-        <v>104914.32</v>
+        <v>107613.89</v>
       </c>
     </row>
     <row r="50">
@@ -5371,13 +5371,13 @@
         <v>-1</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N50" t="n">
-        <v>104914.32</v>
+        <v>107613.89</v>
       </c>
       <c r="O50" t="n">
-        <v>103865.18</v>
+        <v>105921.12</v>
       </c>
     </row>
     <row r="51">
@@ -5428,13 +5428,13 @@
         <v>-1</v>
       </c>
       <c r="M51" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N51" t="n">
         <v>100000</v>
       </c>
       <c r="O51" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="52">
@@ -5485,13 +5485,13 @@
         <v>3.6275</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>3.6275</v>
+        <v>5.706</v>
       </c>
       <c r="N52" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
       <c r="O52" t="n">
-        <v>102591.18</v>
+        <v>104043.23</v>
       </c>
     </row>
     <row r="53">
@@ -5542,13 +5542,13 @@
         <v>-1</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N53" t="n">
         <v>100000</v>
       </c>
       <c r="O53" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="54">
@@ -5599,13 +5599,13 @@
         <v>17.0526</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>17.0526</v>
+        <v>26.8238</v>
       </c>
       <c r="N54" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
       <c r="O54" t="n">
-        <v>115882.11</v>
+        <v>124828.85</v>
       </c>
     </row>
     <row r="55">
@@ -5656,13 +5656,13 @@
         <v>-1</v>
       </c>
       <c r="M55" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N55" t="n">
         <v>100000</v>
       </c>
       <c r="O55" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="56">
@@ -5713,13 +5713,13 @@
         <v>-1</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N56" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
       <c r="O56" t="n">
-        <v>98010</v>
+        <v>96878.74000000001</v>
       </c>
     </row>
     <row r="57">
@@ -5770,13 +5770,13 @@
         <v>-1</v>
       </c>
       <c r="M57" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N57" t="n">
-        <v>98010</v>
+        <v>96878.74000000001</v>
       </c>
       <c r="O57" t="n">
-        <v>97029.89999999999</v>
+        <v>95354.84</v>
       </c>
     </row>
     <row r="58">
@@ -5827,13 +5827,13 @@
         <v>-1</v>
       </c>
       <c r="M58" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N58" t="n">
         <v>100000</v>
       </c>
       <c r="O58" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="59">
@@ -5884,13 +5884,13 @@
         <v>-1</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N59" t="n">
         <v>100000</v>
       </c>
       <c r="O59" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="60">
@@ -5941,13 +5941,13 @@
         <v>-1</v>
       </c>
       <c r="M60" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N60" t="n">
         <v>100000</v>
       </c>
       <c r="O60" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="61">
@@ -5998,13 +5998,13 @@
         <v>-1</v>
       </c>
       <c r="M61" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N61" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
       <c r="O61" t="n">
-        <v>98010</v>
+        <v>96878.74000000001</v>
       </c>
     </row>
     <row r="62">
@@ -6055,13 +6055,13 @@
         <v>-1</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N62" t="n">
-        <v>98010</v>
+        <v>96878.74000000001</v>
       </c>
       <c r="O62" t="n">
-        <v>97029.89999999999</v>
+        <v>95354.84</v>
       </c>
     </row>
     <row r="63">
@@ -6112,13 +6112,13 @@
         <v>-1</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N63" t="n">
-        <v>97029.89999999999</v>
+        <v>95354.84</v>
       </c>
       <c r="O63" t="n">
-        <v>96059.60000000001</v>
+        <v>93854.91</v>
       </c>
     </row>
     <row r="64">
@@ -6169,13 +6169,13 @@
         <v>-1</v>
       </c>
       <c r="M64" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N64" t="n">
-        <v>96059.60000000001</v>
+        <v>93854.91</v>
       </c>
       <c r="O64" t="n">
-        <v>95099</v>
+        <v>92378.57000000001</v>
       </c>
     </row>
     <row r="65">
@@ -6226,13 +6226,13 @@
         <v>-1</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N65" t="n">
         <v>100000</v>
       </c>
       <c r="O65" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="66">
@@ -6283,13 +6283,13 @@
         <v>-1</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N66" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
       <c r="O66" t="n">
-        <v>98010</v>
+        <v>96878.74000000001</v>
       </c>
     </row>
     <row r="67">
@@ -6340,13 +6340,13 @@
         <v>-1</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N67" t="n">
         <v>100000</v>
       </c>
       <c r="O67" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="68">
@@ -6397,13 +6397,13 @@
         <v>-1</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N68" t="n">
         <v>100000</v>
       </c>
       <c r="O68" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="69">
@@ -6454,13 +6454,13 @@
         <v>-1</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N69" t="n">
         <v>100000</v>
       </c>
       <c r="O69" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="70">
@@ -6511,13 +6511,13 @@
         <v>-1</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N70" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
       <c r="O70" t="n">
-        <v>98010</v>
+        <v>96878.74000000001</v>
       </c>
     </row>
     <row r="71">
@@ -6568,13 +6568,13 @@
         <v>1</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1</v>
+        <v>1.573</v>
       </c>
       <c r="N71" t="n">
-        <v>98010</v>
+        <v>96878.74000000001</v>
       </c>
       <c r="O71" t="n">
-        <v>98990.10000000001</v>
+        <v>98402.64999999999</v>
       </c>
     </row>
     <row r="72">
@@ -6625,13 +6625,13 @@
         <v>-1</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N72" t="n">
         <v>100000</v>
       </c>
       <c r="O72" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="73">
@@ -6682,13 +6682,13 @@
         <v>-1</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N73" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
       <c r="O73" t="n">
-        <v>98010</v>
+        <v>96878.74000000001</v>
       </c>
     </row>
     <row r="74">
@@ -6739,13 +6739,13 @@
         <v>-1</v>
       </c>
       <c r="M74" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N74" t="n">
         <v>100000</v>
       </c>
       <c r="O74" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="75">
@@ -6796,13 +6796,13 @@
         <v>-1</v>
       </c>
       <c r="M75" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N75" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
       <c r="O75" t="n">
-        <v>98010</v>
+        <v>96878.74000000001</v>
       </c>
     </row>
     <row r="76">
@@ -6853,13 +6853,13 @@
         <v>-1</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N76" t="n">
-        <v>98010</v>
+        <v>96878.74000000001</v>
       </c>
       <c r="O76" t="n">
-        <v>97029.89999999999</v>
+        <v>95354.84</v>
       </c>
     </row>
     <row r="77">
@@ -6910,13 +6910,13 @@
         <v>-1</v>
       </c>
       <c r="M77" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N77" t="n">
-        <v>97029.89999999999</v>
+        <v>95354.84</v>
       </c>
       <c r="O77" t="n">
-        <v>96059.60000000001</v>
+        <v>93854.91</v>
       </c>
     </row>
     <row r="78">
@@ -6967,13 +6967,13 @@
         <v>-1</v>
       </c>
       <c r="M78" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N78" t="n">
-        <v>96059.60000000001</v>
+        <v>93854.91</v>
       </c>
       <c r="O78" t="n">
-        <v>95099</v>
+        <v>92378.57000000001</v>
       </c>
     </row>
     <row r="79">
@@ -7024,13 +7024,13 @@
         <v>8.0174</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>8.0174</v>
+        <v>12.6114</v>
       </c>
       <c r="N79" t="n">
-        <v>95099</v>
+        <v>92378.57000000001</v>
       </c>
       <c r="O79" t="n">
-        <v>102723.46</v>
+        <v>104028.76</v>
       </c>
     </row>
     <row r="80">
@@ -7081,13 +7081,13 @@
         <v>-1</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N80" t="n">
         <v>100000</v>
       </c>
       <c r="O80" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="81">
@@ -7138,13 +7138,13 @@
         <v>-1</v>
       </c>
       <c r="M81" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N81" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
       <c r="O81" t="n">
-        <v>98010</v>
+        <v>96878.74000000001</v>
       </c>
     </row>
   </sheetData>

--- a/output/slowfix_all_markets_daily.xlsx
+++ b/output/slowfix_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>slowfix daily (target = the first opposite reversal beyond entry, no cap), starting capital 100,000, risk 1.573%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 06:17 UTC.</t>
+          <t>slowfix daily (target = the first opposite reversal beyond entry, no cap), starting capital 100,000, risk 1.573%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 08:10 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/slowfix_all_markets_daily.xlsx
+++ b/output/slowfix_all_markets_daily.xlsx
@@ -582,10 +582,10 @@
         <v>80</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>56.81</v>
+        <v>12.63</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>156805.15</v>
+        <v>112626.25</v>
       </c>
     </row>
     <row r="3">
@@ -630,10 +630,10 @@
         <v>50</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>50.69</v>
+        <v>12.28</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>150690.5</v>
+        <v>112280.28</v>
       </c>
     </row>
     <row r="4">
@@ -678,10 +678,10 @@
         <v>42.9</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>45.56</v>
+        <v>10.73</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>145562.78</v>
+        <v>110726.4</v>
       </c>
     </row>
     <row r="5">
@@ -726,10 +726,10 @@
         <v>33.3</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>30.68</v>
+        <v>7.92</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>130681.67</v>
+        <v>107924.14</v>
       </c>
     </row>
     <row r="6">
@@ -774,10 +774,10 @@
         <v>50</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>24.83</v>
+        <v>6.33</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>124828.85</v>
+        <v>106330.1</v>
       </c>
     </row>
     <row r="7">
@@ -822,10 +822,10 @@
         <v>50</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>15.73</v>
+        <v>4.01</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>115728.42</v>
+        <v>104011.69</v>
       </c>
     </row>
     <row r="8">
@@ -870,10 +870,10 @@
         <v>100</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>9.99</v>
+        <v>3.06</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>109985.13</v>
+        <v>103064.7</v>
       </c>
     </row>
     <row r="9">
@@ -918,16 +918,16 @@
         <v>25</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5.92</v>
+        <v>1.57</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>105921.12</v>
+        <v>101573.31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -942,16 +942,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -963,19 +963,19 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>50</v>
+        <v>16.7</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>4.04</v>
+        <v>1.15</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>104043.23</v>
+        <v>101148.14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -990,16 +990,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1011,13 +1011,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4.03</v>
+        <v>1.03</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>104028.76</v>
+        <v>101034.78</v>
       </c>
     </row>
     <row r="12">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>-1.57</v>
+        <v>-0.4</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="19">
@@ -1380,10 +1380,10 @@
         <v>0</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>-1.57</v>
+        <v>-0.4</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="20">
@@ -1428,10 +1428,10 @@
         <v>0</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>-1.57</v>
+        <v>-0.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="21">
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>-1.57</v>
+        <v>-0.4</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="22">
@@ -1524,10 +1524,10 @@
         <v>0</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>-1.57</v>
+        <v>-0.4</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="23">
@@ -1572,10 +1572,10 @@
         <v>0</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>-3.12</v>
+        <v>-0.79</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>96878.74000000001</v>
+        <v>99209.57000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1620,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>-3.12</v>
+        <v>-0.79</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>96878.74000000001</v>
+        <v>99209.57000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1668,10 +1668,10 @@
         <v>0</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>-4.65</v>
+        <v>-1.18</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>95354.84</v>
+        <v>98816.7</v>
       </c>
     </row>
     <row r="26">
@@ -1716,10 +1716,10 @@
         <v>0</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>-4.65</v>
+        <v>-1.18</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>95354.84</v>
+        <v>98816.7</v>
       </c>
     </row>
     <row r="27">
@@ -1768,10 +1768,10 @@
         <v>50</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>17.27</v>
+        <v>4.35</v>
       </c>
       <c r="N27" s="8" t="n">
-        <v>117266.5</v>
+        <v>104349.21</v>
       </c>
     </row>
     <row r="28">
@@ -1820,10 +1820,10 @@
         <v>33.3</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>13.24</v>
+        <v>3.43</v>
       </c>
       <c r="N28" s="8" t="n">
-        <v>113240.65</v>
+        <v>103427.75</v>
       </c>
     </row>
     <row r="29">
@@ -1872,10 +1872,10 @@
         <v>50</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>5.12</v>
+        <v>1.31</v>
       </c>
       <c r="N29" s="8" t="n">
-        <v>105115.84</v>
+        <v>101308.04</v>
       </c>
     </row>
     <row r="30">
@@ -2231,7 +2231,7 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -2250,40 +2250,40 @@
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="M37" s="10" t="n">
-        <v>-1.57</v>
+        <v>-0.4</v>
       </c>
       <c r="N37" s="8" t="n">
-        <v>98427</v>
+        <v>99602.44</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Teucrium_Wheat_Fund</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -2302,34 +2302,34 @@
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="M38" s="10" t="n">
-        <v>-1.6</v>
+        <v>-0.42</v>
       </c>
       <c r="N38" s="8" t="n">
-        <v>98402.64999999999</v>
+        <v>99582</v>
       </c>
     </row>
     <row r="39">
@@ -2378,16 +2378,16 @@
         <v>0</v>
       </c>
       <c r="M39" s="10" t="n">
-        <v>-3.12</v>
+        <v>-0.79</v>
       </c>
       <c r="N39" s="8" t="n">
-        <v>96878.74000000001</v>
+        <v>99209.57000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>Cocoa_NYCSCE_Futures</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -2409,13 +2409,13 @@
         <v>73</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>0</v>
@@ -2430,16 +2430,16 @@
         <v>0</v>
       </c>
       <c r="M40" s="10" t="n">
-        <v>-3.12</v>
+        <v>-1.18</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>96878.74000000001</v>
+        <v>98816.7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -2461,13 +2461,13 @@
         <v>73</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>0</v>
@@ -2482,16 +2482,16 @@
         <v>0</v>
       </c>
       <c r="M41" s="10" t="n">
-        <v>-4.65</v>
+        <v>-2.79</v>
       </c>
       <c r="N41" s="8" t="n">
-        <v>95354.84</v>
+        <v>97208.83</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>United_States_Oil_Fund_LP</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -2513,13 +2513,13 @@
         <v>73</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I42" s="6" t="n">
         <v>0</v>
@@ -2534,16 +2534,16 @@
         <v>0</v>
       </c>
       <c r="M42" s="10" t="n">
-        <v>-7.62</v>
+        <v>-5</v>
       </c>
       <c r="N42" s="8" t="n">
-        <v>92378.57000000001</v>
+        <v>94997.24000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>slowfix daily (target = the first opposite reversal beyond entry, no cap), starting capital 100,000, risk 1.573%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 08:10 UTC.</t>
+          <t>slowfix daily (target = the first opposite reversal beyond entry, no cap), starting capital 100,000, risk 1.175%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 10:13 UTC.</t>
         </is>
       </c>
     </row>
@@ -2703,13 +2703,13 @@
         <v>-1</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N2" t="n">
         <v>100000</v>
       </c>
       <c r="O2" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="3">
@@ -2760,13 +2760,13 @@
         <v>2.3732</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3.7331</v>
+        <v>0.9398</v>
       </c>
       <c r="N3" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
       <c r="O3" t="n">
-        <v>102101.38</v>
+        <v>100540.08</v>
       </c>
     </row>
     <row r="4">
@@ -2817,13 +2817,13 @@
         <v>10.6094</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>16.6885</v>
+        <v>4.2013</v>
       </c>
       <c r="N4" t="n">
-        <v>102101.38</v>
+        <v>100540.08</v>
       </c>
       <c r="O4" t="n">
-        <v>119140.58</v>
+        <v>104764.07</v>
       </c>
     </row>
     <row r="5">
@@ -2874,13 +2874,13 @@
         <v>-1</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N5" t="n">
-        <v>119140.58</v>
+        <v>104764.07</v>
       </c>
       <c r="O5" t="n">
-        <v>117266.5</v>
+        <v>104349.21</v>
       </c>
     </row>
     <row r="6">
@@ -2931,13 +2931,13 @@
         <v>-1</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N6" t="n">
         <v>100000</v>
       </c>
       <c r="O6" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="7">
@@ -2988,13 +2988,13 @@
         <v>11.1748</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>17.5779</v>
+        <v>4.4252</v>
       </c>
       <c r="N7" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
       <c r="O7" t="n">
-        <v>115728.42</v>
+        <v>104011.69</v>
       </c>
     </row>
     <row r="8">
@@ -3045,13 +3045,13 @@
         <v>6.2472</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>9.8268</v>
+        <v>2.4739</v>
       </c>
       <c r="N8" t="n">
         <v>100000</v>
       </c>
       <c r="O8" t="n">
-        <v>109826.83</v>
+        <v>102473.89</v>
       </c>
     </row>
     <row r="9">
@@ -3102,13 +3102,13 @@
         <v>10.137</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>15.9455</v>
+        <v>4.0142</v>
       </c>
       <c r="N9" t="n">
-        <v>109826.83</v>
+        <v>102473.89</v>
       </c>
       <c r="O9" t="n">
-        <v>127339.25</v>
+        <v>106587.44</v>
       </c>
     </row>
     <row r="10">
@@ -3159,13 +3159,13 @@
         <v>4.9242</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>7.7458</v>
+        <v>1.95</v>
       </c>
       <c r="N10" t="n">
-        <v>127339.25</v>
+        <v>106587.44</v>
       </c>
       <c r="O10" t="n">
-        <v>137202.73</v>
+        <v>108665.9</v>
       </c>
     </row>
     <row r="11">
@@ -3216,13 +3216,13 @@
         <v>10.2439</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>16.1137</v>
+        <v>4.0566</v>
       </c>
       <c r="N11" t="n">
-        <v>137202.73</v>
+        <v>108665.9</v>
       </c>
       <c r="O11" t="n">
-        <v>159311.11</v>
+        <v>113074.02</v>
       </c>
     </row>
     <row r="12">
@@ -3273,13 +3273,13 @@
         <v>-1</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N12" t="n">
-        <v>159311.11</v>
+        <v>113074.02</v>
       </c>
       <c r="O12" t="n">
-        <v>156805.15</v>
+        <v>112626.25</v>
       </c>
     </row>
     <row r="13">
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>156805.15</v>
+        <v>112626.25</v>
       </c>
       <c r="O13" t="n">
-        <v>156805.15</v>
+        <v>112626.25</v>
       </c>
     </row>
     <row r="14">
@@ -3370,13 +3370,13 @@
         <v>-1</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N14" t="n">
         <v>100000</v>
       </c>
       <c r="O14" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="15">
@@ -3427,13 +3427,13 @@
         <v>-1</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N15" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
       <c r="O15" t="n">
-        <v>96878.74000000001</v>
+        <v>99209.57000000001</v>
       </c>
     </row>
     <row r="16">
@@ -3484,13 +3484,13 @@
         <v>-1</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N16" t="n">
-        <v>96878.74000000001</v>
+        <v>99209.57000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>95354.84</v>
+        <v>98816.7</v>
       </c>
     </row>
     <row r="17">
@@ -3541,13 +3541,13 @@
         <v>-1</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N17" t="n">
         <v>100000</v>
       </c>
       <c r="O17" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="18">
@@ -3598,13 +3598,13 @@
         <v>4.3202</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>6.7957</v>
+        <v>1.7108</v>
       </c>
       <c r="N18" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
       <c r="O18" t="n">
-        <v>105115.84</v>
+        <v>101308.04</v>
       </c>
     </row>
     <row r="19">
@@ -3655,13 +3655,13 @@
         <v>-1</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N19" t="n">
         <v>100000</v>
       </c>
       <c r="O19" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="20">
@@ -3712,13 +3712,13 @@
         <v>22.1818</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>34.892</v>
+        <v>8.784000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
       <c r="O20" t="n">
-        <v>132770.15</v>
+        <v>108353.22</v>
       </c>
     </row>
     <row r="21">
@@ -3769,13 +3769,13 @@
         <v>-1</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N21" t="n">
-        <v>132770.15</v>
+        <v>108353.22</v>
       </c>
       <c r="O21" t="n">
-        <v>130681.67</v>
+        <v>107924.14</v>
       </c>
     </row>
     <row r="22">
@@ -3812,10 +3812,10 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>130681.67</v>
+        <v>107924.14</v>
       </c>
       <c r="O22" t="n">
-        <v>130681.67</v>
+        <v>107924.14</v>
       </c>
     </row>
     <row r="23">
@@ -3866,13 +3866,13 @@
         <v>-1</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N23" t="n">
         <v>100000</v>
       </c>
       <c r="O23" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="24">
@@ -3923,13 +3923,13 @@
         <v>-1</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N24" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
       <c r="O24" t="n">
-        <v>96878.74000000001</v>
+        <v>99209.57000000001</v>
       </c>
     </row>
     <row r="25">
@@ -3980,13 +3980,13 @@
         <v>-1</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N25" t="n">
-        <v>96878.74000000001</v>
+        <v>99209.57000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>95354.84</v>
+        <v>98816.7</v>
       </c>
     </row>
     <row r="26">
@@ -4037,13 +4037,13 @@
         <v>-1</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N26" t="n">
         <v>100000</v>
       </c>
       <c r="O26" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="27">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
       <c r="O27" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="28">
@@ -4134,13 +4134,13 @@
         <v>-1</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N28" t="n">
         <v>100000</v>
       </c>
       <c r="O28" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="29">
@@ -4191,13 +4191,13 @@
         <v>-1</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N29" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
       <c r="O29" t="n">
-        <v>96878.74000000001</v>
+        <v>99209.57000000001</v>
       </c>
     </row>
     <row r="30">
@@ -4248,13 +4248,13 @@
         <v>-1</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N30" t="n">
         <v>100000</v>
       </c>
       <c r="O30" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="31">
@@ -4305,13 +4305,13 @@
         <v>10.7368</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>16.8891</v>
+        <v>4.2518</v>
       </c>
       <c r="N31" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
       <c r="O31" t="n">
-        <v>115050.39</v>
+        <v>103838.95</v>
       </c>
     </row>
     <row r="32">
@@ -4362,13 +4362,13 @@
         <v>-1</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N32" t="n">
-        <v>115050.39</v>
+        <v>103838.95</v>
       </c>
       <c r="O32" t="n">
-        <v>113240.65</v>
+        <v>103427.75</v>
       </c>
     </row>
     <row r="33">
@@ -4408,7 +4408,7 @@
         <v>125.6</v>
       </c>
       <c r="J33" t="n">
-        <v>126.01</v>
+        <v>125.69</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4416,16 +4416,16 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>6.3478</v>
+        <v>7.7391</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>9.985099999999999</v>
+        <v>3.0647</v>
       </c>
       <c r="N33" t="n">
         <v>100000</v>
       </c>
       <c r="O33" t="n">
-        <v>109985.13</v>
+        <v>103064.7</v>
       </c>
     </row>
     <row r="34">
@@ -4476,13 +4476,13 @@
         <v>11.506</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>18.099</v>
+        <v>4.5564</v>
       </c>
       <c r="N34" t="n">
         <v>100000</v>
       </c>
       <c r="O34" t="n">
-        <v>118098.98</v>
+        <v>104556.39</v>
       </c>
     </row>
     <row r="35">
@@ -4533,13 +4533,13 @@
         <v>-1</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N35" t="n">
-        <v>118098.98</v>
+        <v>104556.39</v>
       </c>
       <c r="O35" t="n">
-        <v>116241.28</v>
+        <v>104142.34</v>
       </c>
     </row>
     <row r="36">
@@ -4590,13 +4590,13 @@
         <v>4.2457</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>6.6785</v>
+        <v>1.6813</v>
       </c>
       <c r="N36" t="n">
-        <v>116241.28</v>
+        <v>104142.34</v>
       </c>
       <c r="O36" t="n">
-        <v>124004.49</v>
+        <v>105893.3</v>
       </c>
     </row>
     <row r="37">
@@ -4647,13 +4647,13 @@
         <v>14.6875</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>23.1034</v>
+        <v>5.8162</v>
       </c>
       <c r="N37" t="n">
-        <v>124004.49</v>
+        <v>105893.3</v>
       </c>
       <c r="O37" t="n">
-        <v>152653.79</v>
+        <v>112052.32</v>
       </c>
     </row>
     <row r="38">
@@ -4704,13 +4704,13 @@
         <v>-1</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N38" t="n">
-        <v>152653.79</v>
+        <v>112052.32</v>
       </c>
       <c r="O38" t="n">
-        <v>150252.55</v>
+        <v>111608.59</v>
       </c>
     </row>
     <row r="39">
@@ -4761,13 +4761,13 @@
         <v>-1</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N39" t="n">
-        <v>150252.55</v>
+        <v>111608.59</v>
       </c>
       <c r="O39" t="n">
-        <v>147889.07</v>
+        <v>111166.62</v>
       </c>
     </row>
     <row r="40">
@@ -4818,13 +4818,13 @@
         <v>-1</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N40" t="n">
-        <v>147889.07</v>
+        <v>111166.62</v>
       </c>
       <c r="O40" t="n">
-        <v>145562.78</v>
+        <v>110726.4</v>
       </c>
     </row>
     <row r="41">
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>145562.78</v>
+        <v>110726.4</v>
       </c>
       <c r="O41" t="n">
-        <v>145562.78</v>
+        <v>110726.4</v>
       </c>
     </row>
     <row r="42">
@@ -4915,13 +4915,13 @@
         <v>-1</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N42" t="n">
         <v>100000</v>
       </c>
       <c r="O42" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="43">
@@ -4972,13 +4972,13 @@
         <v>-1</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N43" t="n">
         <v>100000</v>
       </c>
       <c r="O43" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="44">
@@ -5029,13 +5029,13 @@
         <v>25.8788</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>40.7073</v>
+        <v>10.248</v>
       </c>
       <c r="N44" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
       <c r="O44" t="n">
-        <v>138494.01</v>
+        <v>109811.42</v>
       </c>
     </row>
     <row r="45">
@@ -5086,13 +5086,13 @@
         <v>6.704</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>10.5454</v>
+        <v>2.6548</v>
       </c>
       <c r="N45" t="n">
-        <v>138494.01</v>
+        <v>109811.42</v>
       </c>
       <c r="O45" t="n">
-        <v>153098.74</v>
+        <v>112726.67</v>
       </c>
     </row>
     <row r="46">
@@ -5143,13 +5143,13 @@
         <v>-1</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N46" t="n">
-        <v>153098.74</v>
+        <v>112726.67</v>
       </c>
       <c r="O46" t="n">
-        <v>150690.5</v>
+        <v>112280.28</v>
       </c>
     </row>
     <row r="47">
@@ -5200,13 +5200,13 @@
         <v>-1</v>
       </c>
       <c r="M47" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N47" t="n">
         <v>100000</v>
       </c>
       <c r="O47" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="48">
@@ -5257,13 +5257,13 @@
         <v>-1</v>
       </c>
       <c r="M48" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N48" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
       <c r="O48" t="n">
-        <v>96878.74000000001</v>
+        <v>99209.57000000001</v>
       </c>
     </row>
     <row r="49">
@@ -5314,13 +5314,13 @@
         <v>7.0445</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>11.081</v>
+        <v>2.7896</v>
       </c>
       <c r="N49" t="n">
-        <v>96878.74000000001</v>
+        <v>99209.57000000001</v>
       </c>
       <c r="O49" t="n">
-        <v>107613.89</v>
+        <v>101977.14</v>
       </c>
     </row>
     <row r="50">
@@ -5371,13 +5371,13 @@
         <v>-1</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N50" t="n">
-        <v>107613.89</v>
+        <v>101977.14</v>
       </c>
       <c r="O50" t="n">
-        <v>105921.12</v>
+        <v>101573.31</v>
       </c>
     </row>
     <row r="51">
@@ -5428,13 +5428,13 @@
         <v>-1</v>
       </c>
       <c r="M51" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N51" t="n">
         <v>100000</v>
       </c>
       <c r="O51" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="52">
@@ -5485,13 +5485,13 @@
         <v>3.6275</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>5.706</v>
+        <v>1.4365</v>
       </c>
       <c r="N52" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
       <c r="O52" t="n">
-        <v>104043.23</v>
+        <v>101034.78</v>
       </c>
     </row>
     <row r="53">
@@ -5542,13 +5542,13 @@
         <v>-1</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N53" t="n">
         <v>100000</v>
       </c>
       <c r="O53" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="54">
@@ -5599,13 +5599,13 @@
         <v>17.0526</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>26.8238</v>
+        <v>6.7528</v>
       </c>
       <c r="N54" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
       <c r="O54" t="n">
-        <v>124828.85</v>
+        <v>106330.1</v>
       </c>
     </row>
     <row r="55">
@@ -5656,13 +5656,13 @@
         <v>-1</v>
       </c>
       <c r="M55" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N55" t="n">
         <v>100000</v>
       </c>
       <c r="O55" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="56">
@@ -5713,13 +5713,13 @@
         <v>-1</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N56" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
       <c r="O56" t="n">
-        <v>96878.74000000001</v>
+        <v>99209.57000000001</v>
       </c>
     </row>
     <row r="57">
@@ -5770,13 +5770,13 @@
         <v>-1</v>
       </c>
       <c r="M57" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N57" t="n">
-        <v>96878.74000000001</v>
+        <v>99209.57000000001</v>
       </c>
       <c r="O57" t="n">
-        <v>95354.84</v>
+        <v>98816.7</v>
       </c>
     </row>
     <row r="58">
@@ -5827,13 +5827,13 @@
         <v>-1</v>
       </c>
       <c r="M58" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N58" t="n">
         <v>100000</v>
       </c>
       <c r="O58" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="59">
@@ -5884,13 +5884,13 @@
         <v>-1</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N59" t="n">
         <v>100000</v>
       </c>
       <c r="O59" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="60">
@@ -5941,13 +5941,13 @@
         <v>-1</v>
       </c>
       <c r="M60" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N60" t="n">
         <v>100000</v>
       </c>
       <c r="O60" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="61">
@@ -5987,7 +5987,7 @@
         <v>6792.5</v>
       </c>
       <c r="J61" t="n">
-        <v>6988.83</v>
+        <v>7002</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5995,16 +5995,16 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>-1</v>
+        <v>-3.0482</v>
       </c>
       <c r="M61" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.2071</v>
       </c>
       <c r="N61" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
       <c r="O61" t="n">
-        <v>96878.74000000001</v>
+        <v>98401.69</v>
       </c>
     </row>
     <row r="62">
@@ -6055,13 +6055,13 @@
         <v>-1</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N62" t="n">
-        <v>96878.74000000001</v>
+        <v>98401.69</v>
       </c>
       <c r="O62" t="n">
-        <v>95354.84</v>
+        <v>98012.02</v>
       </c>
     </row>
     <row r="63">
@@ -6112,13 +6112,13 @@
         <v>-1</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N63" t="n">
-        <v>95354.84</v>
+        <v>98012.02</v>
       </c>
       <c r="O63" t="n">
-        <v>93854.91</v>
+        <v>97623.89</v>
       </c>
     </row>
     <row r="64">
@@ -6158,7 +6158,7 @@
         <v>6964.1</v>
       </c>
       <c r="J64" t="n">
-        <v>6770.77</v>
+        <v>6769.03</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -6166,16 +6166,16 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>-1</v>
+        <v>-1.0736</v>
       </c>
       <c r="M64" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.4252</v>
       </c>
       <c r="N64" t="n">
-        <v>93854.91</v>
+        <v>97623.89</v>
       </c>
       <c r="O64" t="n">
-        <v>92378.57000000001</v>
+        <v>97208.83</v>
       </c>
     </row>
     <row r="65">
@@ -6226,13 +6226,13 @@
         <v>-1</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N65" t="n">
         <v>100000</v>
       </c>
       <c r="O65" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="66">
@@ -6283,13 +6283,13 @@
         <v>-1</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N66" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
       <c r="O66" t="n">
-        <v>96878.74000000001</v>
+        <v>99209.57000000001</v>
       </c>
     </row>
     <row r="67">
@@ -6340,13 +6340,13 @@
         <v>-1</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N67" t="n">
         <v>100000</v>
       </c>
       <c r="O67" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="68">
@@ -6386,7 +6386,7 @@
         <v>19.9</v>
       </c>
       <c r="J68" t="n">
-        <v>21.07</v>
+        <v>21.08</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -6394,16 +6394,16 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>-1</v>
+        <v>-1.0556</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.418</v>
       </c>
       <c r="N68" t="n">
         <v>100000</v>
       </c>
       <c r="O68" t="n">
-        <v>98427</v>
+        <v>99582</v>
       </c>
     </row>
     <row r="69">
@@ -6454,13 +6454,13 @@
         <v>-1</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N69" t="n">
         <v>100000</v>
       </c>
       <c r="O69" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="70">
@@ -6511,13 +6511,13 @@
         <v>-1</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N70" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
       <c r="O70" t="n">
-        <v>96878.74000000001</v>
+        <v>99209.57000000001</v>
       </c>
     </row>
     <row r="71">
@@ -6568,13 +6568,13 @@
         <v>1</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1.573</v>
+        <v>0.396</v>
       </c>
       <c r="N71" t="n">
-        <v>96878.74000000001</v>
+        <v>99209.57000000001</v>
       </c>
       <c r="O71" t="n">
-        <v>98402.64999999999</v>
+        <v>99602.44</v>
       </c>
     </row>
     <row r="72">
@@ -6625,13 +6625,13 @@
         <v>-1</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N72" t="n">
         <v>100000</v>
       </c>
       <c r="O72" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="73">
@@ -6682,13 +6682,13 @@
         <v>-1</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N73" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
       <c r="O73" t="n">
-        <v>96878.74000000001</v>
+        <v>99209.57000000001</v>
       </c>
     </row>
     <row r="74">
@@ -6739,13 +6739,13 @@
         <v>-1</v>
       </c>
       <c r="M74" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N74" t="n">
         <v>100000</v>
       </c>
       <c r="O74" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="75">
@@ -6796,13 +6796,13 @@
         <v>-1</v>
       </c>
       <c r="M75" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N75" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
       <c r="O75" t="n">
-        <v>96878.74000000001</v>
+        <v>99209.57000000001</v>
       </c>
     </row>
     <row r="76">
@@ -6853,13 +6853,13 @@
         <v>-1</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N76" t="n">
-        <v>96878.74000000001</v>
+        <v>99209.57000000001</v>
       </c>
       <c r="O76" t="n">
-        <v>95354.84</v>
+        <v>98816.7</v>
       </c>
     </row>
     <row r="77">
@@ -6910,13 +6910,13 @@
         <v>-1</v>
       </c>
       <c r="M77" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N77" t="n">
-        <v>95354.84</v>
+        <v>98816.7</v>
       </c>
       <c r="O77" t="n">
-        <v>93854.91</v>
+        <v>98425.38</v>
       </c>
     </row>
     <row r="78">
@@ -6967,13 +6967,13 @@
         <v>-1</v>
       </c>
       <c r="M78" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N78" t="n">
-        <v>93854.91</v>
+        <v>98425.38</v>
       </c>
       <c r="O78" t="n">
-        <v>92378.57000000001</v>
+        <v>98035.62</v>
       </c>
     </row>
     <row r="79">
@@ -7024,13 +7024,13 @@
         <v>8.0174</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>12.6114</v>
+        <v>3.1749</v>
       </c>
       <c r="N79" t="n">
-        <v>92378.57000000001</v>
+        <v>98035.62</v>
       </c>
       <c r="O79" t="n">
-        <v>104028.76</v>
+        <v>101148.14</v>
       </c>
     </row>
     <row r="80">
@@ -7081,13 +7081,13 @@
         <v>-1</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.396</v>
       </c>
       <c r="N80" t="n">
         <v>100000</v>
       </c>
       <c r="O80" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
     </row>
     <row r="81">
@@ -7127,7 +7127,7 @@
         <v>98.3</v>
       </c>
       <c r="J81" t="n">
-        <v>130.94</v>
+        <v>139.27</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -7135,16 +7135,16 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>-1</v>
+        <v>-11.6795</v>
       </c>
       <c r="M81" s="5" t="n">
-        <v>-1.573</v>
+        <v>-4.6251</v>
       </c>
       <c r="N81" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
       <c r="O81" t="n">
-        <v>96878.74000000001</v>
+        <v>94997.24000000001</v>
       </c>
     </row>
   </sheetData>

--- a/output/slowfix_all_markets_daily.xlsx
+++ b/output/slowfix_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>slowfix daily (target = the first opposite reversal beyond entry, no cap), starting capital 100,000, risk 1.175%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 10:13 UTC.</t>
+          <t>slowfix daily (target = the first opposite reversal beyond entry, no cap), starting capital 100,000, risk 1.175%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 19:13 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/slowfix_all_markets_daily.xlsx
+++ b/output/slowfix_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>slowfix daily (target = the first opposite reversal beyond entry, no cap), starting capital 100,000, risk 1.175%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 19:13 UTC.</t>
+          <t>slowfix daily (target = the first opposite reversal beyond entry, no cap), starting capital 100,000, risk 1.175%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 20:58 UTC.</t>
         </is>
       </c>
     </row>
